--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460794</v>
+        <v>122460934</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>57749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566775</v>
+        <v>566622</v>
       </c>
       <c r="R2" t="n">
-        <v>6417541</v>
+        <v>6417518</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460344</v>
+        <v>122460478</v>
       </c>
       <c r="B3" t="n">
         <v>98197</v>
@@ -837,7 +840,7 @@
         <v>566761</v>
       </c>
       <c r="R3" t="n">
-        <v>6417474</v>
+        <v>6417508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460478</v>
+        <v>122460427</v>
       </c>
       <c r="B4" t="n">
         <v>98197</v>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566761</v>
+        <v>566763</v>
       </c>
       <c r="R4" t="n">
-        <v>6417508</v>
+        <v>6417499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460839</v>
+        <v>122460716</v>
       </c>
       <c r="B5" t="n">
         <v>98197</v>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566801</v>
+        <v>566691</v>
       </c>
       <c r="R5" t="n">
-        <v>6417510</v>
+        <v>6417494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460716</v>
+        <v>122460754</v>
       </c>
       <c r="B6" t="n">
         <v>98197</v>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566691</v>
+        <v>566688</v>
       </c>
       <c r="R6" t="n">
-        <v>6417494</v>
+        <v>6417499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460760</v>
+        <v>122460731</v>
       </c>
       <c r="B7" t="n">
         <v>98197</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566688</v>
+        <v>566693</v>
       </c>
       <c r="R7" t="n">
-        <v>6417511</v>
+        <v>6417493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460434</v>
+        <v>122460363</v>
       </c>
       <c r="B8" t="n">
         <v>98197</v>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566795</v>
+        <v>566758</v>
       </c>
       <c r="R8" t="n">
-        <v>6417518</v>
+        <v>6417476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460830</v>
+        <v>122460581</v>
       </c>
       <c r="B9" t="n">
         <v>98197</v>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566776</v>
+        <v>566740</v>
       </c>
       <c r="R9" t="n">
-        <v>6417537</v>
+        <v>6417531</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460572</v>
+        <v>122460310</v>
       </c>
       <c r="B10" t="n">
         <v>98197</v>
@@ -1602,7 +1605,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1611,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566746</v>
+        <v>566794</v>
       </c>
       <c r="R10" t="n">
-        <v>6417537</v>
+        <v>6417463</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1785,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460411</v>
+        <v>122460839</v>
       </c>
       <c r="B12" t="n">
         <v>98197</v>
@@ -1833,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566756</v>
+        <v>566801</v>
       </c>
       <c r="R12" t="n">
-        <v>6417478</v>
+        <v>6417510</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460353</v>
+        <v>122460411</v>
       </c>
       <c r="B13" t="n">
         <v>98197</v>
@@ -1944,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566758</v>
+        <v>566756</v>
       </c>
       <c r="R13" t="n">
-        <v>6417479</v>
+        <v>6417478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460462</v>
+        <v>122460769</v>
       </c>
       <c r="B14" t="n">
         <v>98197</v>
@@ -2055,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566759</v>
+        <v>566727</v>
       </c>
       <c r="R14" t="n">
-        <v>6417510</v>
+        <v>6417559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2125,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460731</v>
+        <v>122460491</v>
       </c>
       <c r="B15" t="n">
         <v>98197</v>
@@ -2166,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566693</v>
+        <v>566757</v>
       </c>
       <c r="R15" t="n">
-        <v>6417493</v>
+        <v>6417517</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2236,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460919</v>
+        <v>122460727</v>
       </c>
       <c r="B16" t="n">
         <v>98197</v>
@@ -2277,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566772</v>
+        <v>566693</v>
       </c>
       <c r="R16" t="n">
-        <v>6417498</v>
+        <v>6417494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2347,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460786</v>
+        <v>122460462</v>
       </c>
       <c r="B17" t="n">
         <v>98197</v>
@@ -2388,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566755</v>
+        <v>566759</v>
       </c>
       <c r="R17" t="n">
-        <v>6417553</v>
+        <v>6417510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2458,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460769</v>
+        <v>122460558</v>
       </c>
       <c r="B18" t="n">
         <v>98197</v>
@@ -2499,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566727</v>
+        <v>566735</v>
       </c>
       <c r="R18" t="n">
-        <v>6417559</v>
+        <v>6417522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2569,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460581</v>
+        <v>122460919</v>
       </c>
       <c r="B19" t="n">
         <v>98197</v>
@@ -2610,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566740</v>
+        <v>566772</v>
       </c>
       <c r="R19" t="n">
-        <v>6417531</v>
+        <v>6417498</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2680,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460427</v>
+        <v>122460450</v>
       </c>
       <c r="B20" t="n">
         <v>98197</v>
@@ -2721,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R20" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2791,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460400</v>
+        <v>122460344</v>
       </c>
       <c r="B21" t="n">
         <v>98197</v>
@@ -2832,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566747</v>
+        <v>566761</v>
       </c>
       <c r="R21" t="n">
-        <v>6417470</v>
+        <v>6417474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,10 +2902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460558</v>
+        <v>122460743</v>
       </c>
       <c r="B22" t="n">
-        <v>98197</v>
+        <v>91206</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2907,35 +2914,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2943,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566735</v>
+        <v>566698</v>
       </c>
       <c r="R22" t="n">
-        <v>6417522</v>
+        <v>6417489</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3016,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460545</v>
+        <v>122460440</v>
       </c>
       <c r="B23" t="n">
         <v>98197</v>
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566762</v>
+        <v>566775</v>
       </c>
       <c r="R23" t="n">
-        <v>6417537</v>
+        <v>6417497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3117,7 +3127,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460754</v>
+        <v>122460916</v>
       </c>
       <c r="B24" t="n">
         <v>98197</v>
@@ -3165,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566688</v>
+        <v>566783</v>
       </c>
       <c r="R24" t="n">
-        <v>6417499</v>
+        <v>6417513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460363</v>
+        <v>122460929</v>
       </c>
       <c r="B25" t="n">
-        <v>98197</v>
+        <v>57532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3240,35 +3250,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3276,13 +3290,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566758</v>
+        <v>566622</v>
       </c>
       <c r="R25" t="n">
-        <v>6417476</v>
+        <v>6417518</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3320,7 +3334,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3339,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460929</v>
+        <v>122460353</v>
       </c>
       <c r="B26" t="n">
-        <v>57532</v>
+        <v>98197</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3351,39 +3364,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3391,13 +3400,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566622</v>
+        <v>566758</v>
       </c>
       <c r="R26" t="n">
-        <v>6417518</v>
+        <v>6417479</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3435,6 +3444,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3453,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460743</v>
+        <v>122460522</v>
       </c>
       <c r="B27" t="n">
-        <v>91206</v>
+        <v>98197</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3465,38 +3475,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3504,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566698</v>
+        <v>566762</v>
       </c>
       <c r="R27" t="n">
-        <v>6417489</v>
+        <v>6417537</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,7 +3578,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460491</v>
+        <v>122460572</v>
       </c>
       <c r="B28" t="n">
         <v>98197</v>
@@ -3615,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566757</v>
+        <v>566746</v>
       </c>
       <c r="R28" t="n">
-        <v>6417517</v>
+        <v>6417537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3678,7 +3689,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460450</v>
+        <v>122460434</v>
       </c>
       <c r="B29" t="n">
         <v>98197</v>
@@ -3726,10 +3737,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566761</v>
+        <v>566795</v>
       </c>
       <c r="R29" t="n">
-        <v>6417502</v>
+        <v>6417518</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3800,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460440</v>
+        <v>122460400</v>
       </c>
       <c r="B30" t="n">
         <v>98197</v>
@@ -3837,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566775</v>
+        <v>566747</v>
       </c>
       <c r="R30" t="n">
-        <v>6417497</v>
+        <v>6417470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3900,7 +3911,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460727</v>
+        <v>122460760</v>
       </c>
       <c r="B31" t="n">
         <v>98197</v>
@@ -3948,10 +3959,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566693</v>
+        <v>566688</v>
       </c>
       <c r="R31" t="n">
-        <v>6417494</v>
+        <v>6417511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4011,7 +4022,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460916</v>
+        <v>122460794</v>
       </c>
       <c r="B32" t="n">
         <v>98197</v>
@@ -4059,10 +4070,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566783</v>
+        <v>566775</v>
       </c>
       <c r="R32" t="n">
-        <v>6417513</v>
+        <v>6417541</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4122,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460934</v>
+        <v>122460786</v>
       </c>
       <c r="B33" t="n">
-        <v>57749</v>
+        <v>98197</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4134,39 +4145,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4174,13 +4181,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566622</v>
+        <v>566755</v>
       </c>
       <c r="R33" t="n">
-        <v>6417518</v>
+        <v>6417553</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4218,6 +4225,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4236,7 +4244,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460310</v>
+        <v>122460830</v>
       </c>
       <c r="B34" t="n">
         <v>98197</v>
@@ -4275,11 +4283,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566794</v>
+        <v>566776</v>
       </c>
       <c r="R34" t="n">
-        <v>6417463</v>
+        <v>6417537</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460934</v>
+        <v>122460491</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566622</v>
+        <v>566757</v>
       </c>
       <c r="R2" t="n">
-        <v>6417518</v>
+        <v>6417517</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460478</v>
+        <v>122460743</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>91211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566761</v>
+        <v>566698</v>
       </c>
       <c r="R3" t="n">
-        <v>6417508</v>
+        <v>6417489</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460427</v>
+        <v>122460731</v>
       </c>
       <c r="B4" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566763</v>
+        <v>566693</v>
       </c>
       <c r="R4" t="n">
-        <v>6417499</v>
+        <v>6417493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460716</v>
+        <v>122460727</v>
       </c>
       <c r="B5" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566691</v>
+        <v>566693</v>
       </c>
       <c r="R5" t="n">
         <v>6417494</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460754</v>
+        <v>122460929</v>
       </c>
       <c r="B6" t="n">
-        <v>98197</v>
+        <v>57532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566688</v>
+        <v>566622</v>
       </c>
       <c r="R6" t="n">
-        <v>6417499</v>
+        <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460731</v>
+        <v>122460411</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566693</v>
+        <v>566756</v>
       </c>
       <c r="R7" t="n">
-        <v>6417493</v>
+        <v>6417478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460363</v>
+        <v>122460434</v>
       </c>
       <c r="B8" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566758</v>
+        <v>566795</v>
       </c>
       <c r="R8" t="n">
-        <v>6417476</v>
+        <v>6417518</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460581</v>
+        <v>122460400</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566740</v>
+        <v>566747</v>
       </c>
       <c r="R9" t="n">
-        <v>6417531</v>
+        <v>6417470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460310</v>
+        <v>122460427</v>
       </c>
       <c r="B10" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,11 +1608,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1618,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566794</v>
+        <v>566763</v>
       </c>
       <c r="R10" t="n">
-        <v>6417463</v>
+        <v>6417499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460420</v>
+        <v>122460440</v>
       </c>
       <c r="B11" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566778</v>
+        <v>566775</v>
       </c>
       <c r="R11" t="n">
-        <v>6417475</v>
+        <v>6417497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1794,7 @@
         <v>122460839</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1903,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460411</v>
+        <v>122460581</v>
       </c>
       <c r="B13" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566756</v>
+        <v>566740</v>
       </c>
       <c r="R13" t="n">
-        <v>6417478</v>
+        <v>6417531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460769</v>
+        <v>122460830</v>
       </c>
       <c r="B14" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566727</v>
+        <v>566776</v>
       </c>
       <c r="R14" t="n">
-        <v>6417559</v>
+        <v>6417537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460491</v>
+        <v>122460769</v>
       </c>
       <c r="B15" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566757</v>
+        <v>566727</v>
       </c>
       <c r="R15" t="n">
-        <v>6417517</v>
+        <v>6417559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460727</v>
+        <v>122460919</v>
       </c>
       <c r="B16" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566693</v>
+        <v>566772</v>
       </c>
       <c r="R16" t="n">
-        <v>6417494</v>
+        <v>6417498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460462</v>
+        <v>122460450</v>
       </c>
       <c r="B17" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566759</v>
+        <v>566761</v>
       </c>
       <c r="R17" t="n">
-        <v>6417510</v>
+        <v>6417502</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460558</v>
+        <v>122460760</v>
       </c>
       <c r="B18" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2506,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566735</v>
+        <v>566688</v>
       </c>
       <c r="R18" t="n">
-        <v>6417522</v>
+        <v>6417511</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460919</v>
+        <v>122460716</v>
       </c>
       <c r="B19" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566772</v>
+        <v>566691</v>
       </c>
       <c r="R19" t="n">
-        <v>6417498</v>
+        <v>6417494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460450</v>
+        <v>122460344</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2731,7 +2730,7 @@
         <v>566761</v>
       </c>
       <c r="R20" t="n">
-        <v>6417502</v>
+        <v>6417474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460344</v>
+        <v>122460509</v>
       </c>
       <c r="B21" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566761</v>
+        <v>566762</v>
       </c>
       <c r="R21" t="n">
-        <v>6417474</v>
+        <v>6417537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460743</v>
+        <v>122460462</v>
       </c>
       <c r="B22" t="n">
-        <v>91206</v>
+        <v>98202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,38 +2913,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2953,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566698</v>
+        <v>566759</v>
       </c>
       <c r="R22" t="n">
-        <v>6417489</v>
+        <v>6417510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3012,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460440</v>
+        <v>122460478</v>
       </c>
       <c r="B23" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566775</v>
+        <v>566761</v>
       </c>
       <c r="R23" t="n">
-        <v>6417497</v>
+        <v>6417508</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460916</v>
+        <v>122460754</v>
       </c>
       <c r="B24" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566783</v>
+        <v>566688</v>
       </c>
       <c r="R24" t="n">
-        <v>6417513</v>
+        <v>6417499</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460929</v>
+        <v>122460363</v>
       </c>
       <c r="B25" t="n">
-        <v>57532</v>
+        <v>98202</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3250,39 +3246,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3290,13 +3282,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566622</v>
+        <v>566758</v>
       </c>
       <c r="R25" t="n">
-        <v>6417518</v>
+        <v>6417476</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,6 +3326,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3352,10 +3345,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460353</v>
+        <v>122460310</v>
       </c>
       <c r="B26" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,7 +3384,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3400,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566758</v>
+        <v>566794</v>
       </c>
       <c r="R26" t="n">
-        <v>6417479</v>
+        <v>6417463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460522</v>
+        <v>122460934</v>
       </c>
       <c r="B27" t="n">
-        <v>98197</v>
+        <v>57749</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3475,39 +3472,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3515,13 +3512,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566762</v>
+        <v>566622</v>
       </c>
       <c r="R27" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,7 +3556,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3578,10 +3574,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460572</v>
+        <v>122460558</v>
       </c>
       <c r="B28" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3626,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566746</v>
+        <v>566735</v>
       </c>
       <c r="R28" t="n">
-        <v>6417537</v>
+        <v>6417522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460434</v>
+        <v>122460420</v>
       </c>
       <c r="B29" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566795</v>
+        <v>566778</v>
       </c>
       <c r="R29" t="n">
-        <v>6417518</v>
+        <v>6417475</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460400</v>
+        <v>122460916</v>
       </c>
       <c r="B30" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3848,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566747</v>
+        <v>566783</v>
       </c>
       <c r="R30" t="n">
-        <v>6417470</v>
+        <v>6417513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,10 +3907,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460760</v>
+        <v>122460572</v>
       </c>
       <c r="B31" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566688</v>
+        <v>566746</v>
       </c>
       <c r="R31" t="n">
-        <v>6417511</v>
+        <v>6417537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4021,7 @@
         <v>122460794</v>
       </c>
       <c r="B32" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4133,10 +4129,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460786</v>
+        <v>122460353</v>
       </c>
       <c r="B33" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566755</v>
+        <v>566758</v>
       </c>
       <c r="R33" t="n">
-        <v>6417553</v>
+        <v>6417479</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460830</v>
+        <v>122460786</v>
       </c>
       <c r="B34" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566776</v>
+        <v>566755</v>
       </c>
       <c r="R34" t="n">
-        <v>6417537</v>
+        <v>6417553</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460491</v>
+        <v>122460353</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566757</v>
+        <v>566758</v>
       </c>
       <c r="R2" t="n">
-        <v>6417517</v>
+        <v>6417479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460743</v>
+        <v>122460363</v>
       </c>
       <c r="B3" t="n">
-        <v>91211</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566698</v>
+        <v>566758</v>
       </c>
       <c r="R3" t="n">
-        <v>6417489</v>
+        <v>6417476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460731</v>
+        <v>122460754</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,11 +904,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -948,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566693</v>
+        <v>566688</v>
       </c>
       <c r="R4" t="n">
-        <v>6417493</v>
+        <v>6417499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460727</v>
+        <v>122460509</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,11 +1010,6 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1059,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566693</v>
+        <v>566762</v>
       </c>
       <c r="R5" t="n">
-        <v>6417494</v>
+        <v>6417537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460929</v>
+        <v>122460716</v>
       </c>
       <c r="B6" t="n">
-        <v>57532</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1111,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566622</v>
+        <v>566691</v>
       </c>
       <c r="R6" t="n">
-        <v>6417518</v>
+        <v>6417494</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1186,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460411</v>
+        <v>122460478</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,11 +1222,6 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1284,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566756</v>
+        <v>566761</v>
       </c>
       <c r="R7" t="n">
-        <v>6417478</v>
+        <v>6417508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460434</v>
+        <v>122460581</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,11 +1328,6 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1395,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566795</v>
+        <v>566740</v>
       </c>
       <c r="R8" t="n">
-        <v>6417518</v>
+        <v>6417531</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460400</v>
+        <v>122460440</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,11 +1434,6 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1506,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566747</v>
+        <v>566775</v>
       </c>
       <c r="R9" t="n">
-        <v>6417470</v>
+        <v>6417497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460427</v>
+        <v>122460839</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,11 +1540,6 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1617,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566763</v>
+        <v>566801</v>
       </c>
       <c r="R10" t="n">
-        <v>6417499</v>
+        <v>6417510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460440</v>
+        <v>122460411</v>
       </c>
       <c r="B11" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,11 +1646,6 @@
       </c>
       <c r="E11" t="n">
         <v>220787</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1728,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566775</v>
+        <v>566756</v>
       </c>
       <c r="R11" t="n">
-        <v>6417497</v>
+        <v>6417478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460839</v>
+        <v>122460450</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,11 +1752,6 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1839,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566801</v>
+        <v>566761</v>
       </c>
       <c r="R12" t="n">
-        <v>6417510</v>
+        <v>6417502</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460581</v>
+        <v>122460830</v>
       </c>
       <c r="B13" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,11 +1858,6 @@
       </c>
       <c r="E13" t="n">
         <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1950,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566740</v>
+        <v>566776</v>
       </c>
       <c r="R13" t="n">
-        <v>6417531</v>
+        <v>6417537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460830</v>
+        <v>122460572</v>
       </c>
       <c r="B14" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,11 +1964,6 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2061,7 +1990,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566776</v>
+        <v>566746</v>
       </c>
       <c r="R14" t="n">
         <v>6417537</v>
@@ -2124,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460769</v>
+        <v>122460794</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,11 +2070,6 @@
       </c>
       <c r="E15" t="n">
         <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2172,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566727</v>
+        <v>566775</v>
       </c>
       <c r="R15" t="n">
-        <v>6417559</v>
+        <v>6417541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460919</v>
+        <v>122460786</v>
       </c>
       <c r="B16" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2252,11 +2176,6 @@
       </c>
       <c r="E16" t="n">
         <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2283,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566772</v>
+        <v>566755</v>
       </c>
       <c r="R16" t="n">
-        <v>6417498</v>
+        <v>6417553</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460450</v>
+        <v>122460558</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,11 +2282,6 @@
       </c>
       <c r="E17" t="n">
         <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2394,10 +2308,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566761</v>
+        <v>566735</v>
       </c>
       <c r="R17" t="n">
-        <v>6417502</v>
+        <v>6417522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460760</v>
+        <v>122460929</v>
       </c>
       <c r="B18" t="n">
-        <v>98202</v>
+        <v>57532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2469,35 +2383,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2505,13 +2418,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566688</v>
+        <v>566622</v>
       </c>
       <c r="R18" t="n">
-        <v>6417511</v>
+        <v>6417518</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2549,7 +2462,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2568,10 +2480,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460716</v>
+        <v>122460310</v>
       </c>
       <c r="B19" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2586,11 +2498,6 @@
       <c r="E19" t="n">
         <v>220787</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2607,7 +2514,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2616,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566691</v>
+        <v>566794</v>
       </c>
       <c r="R19" t="n">
-        <v>6417494</v>
+        <v>6417463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,10 +2590,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460344</v>
+        <v>122460427</v>
       </c>
       <c r="B20" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,11 +2607,6 @@
       </c>
       <c r="E20" t="n">
         <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2727,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566761</v>
+        <v>566763</v>
       </c>
       <c r="R20" t="n">
-        <v>6417474</v>
+        <v>6417499</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460509</v>
+        <v>122460462</v>
       </c>
       <c r="B21" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,11 +2713,6 @@
       </c>
       <c r="E21" t="n">
         <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2838,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566762</v>
+        <v>566759</v>
       </c>
       <c r="R21" t="n">
-        <v>6417537</v>
+        <v>6417510</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,10 +2802,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460462</v>
+        <v>122460344</v>
       </c>
       <c r="B22" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2918,11 +2819,6 @@
       </c>
       <c r="E22" t="n">
         <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2949,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566759</v>
+        <v>566761</v>
       </c>
       <c r="R22" t="n">
-        <v>6417510</v>
+        <v>6417474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,10 +2908,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460478</v>
+        <v>122460727</v>
       </c>
       <c r="B23" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3029,11 +2925,6 @@
       </c>
       <c r="E23" t="n">
         <v>220787</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3060,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566761</v>
+        <v>566693</v>
       </c>
       <c r="R23" t="n">
-        <v>6417508</v>
+        <v>6417494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,10 +3014,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460754</v>
+        <v>122460434</v>
       </c>
       <c r="B24" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,11 +3031,6 @@
       </c>
       <c r="E24" t="n">
         <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3171,10 +3057,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566688</v>
+        <v>566795</v>
       </c>
       <c r="R24" t="n">
-        <v>6417499</v>
+        <v>6417518</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460363</v>
+        <v>122460420</v>
       </c>
       <c r="B25" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3251,11 +3137,6 @@
       </c>
       <c r="E25" t="n">
         <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3282,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566758</v>
+        <v>566778</v>
       </c>
       <c r="R25" t="n">
-        <v>6417476</v>
+        <v>6417475</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460310</v>
+        <v>122460916</v>
       </c>
       <c r="B26" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3363,11 +3244,6 @@
       <c r="E26" t="n">
         <v>220787</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -3384,11 +3260,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3397,10 +3269,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566794</v>
+        <v>566783</v>
       </c>
       <c r="R26" t="n">
-        <v>6417463</v>
+        <v>6417513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,10 +3332,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460934</v>
+        <v>122460760</v>
       </c>
       <c r="B27" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3472,39 +3344,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3512,13 +3375,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566622</v>
+        <v>566688</v>
       </c>
       <c r="R27" t="n">
-        <v>6417518</v>
+        <v>6417511</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3556,6 +3419,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3574,10 +3438,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460558</v>
+        <v>122460491</v>
       </c>
       <c r="B28" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3591,11 +3455,6 @@
       </c>
       <c r="E28" t="n">
         <v>220787</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3622,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566735</v>
+        <v>566757</v>
       </c>
       <c r="R28" t="n">
-        <v>6417522</v>
+        <v>6417517</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,10 +3544,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460420</v>
+        <v>122460934</v>
       </c>
       <c r="B29" t="n">
-        <v>98202</v>
+        <v>57749</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3697,35 +3556,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3733,13 +3591,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566778</v>
+        <v>566622</v>
       </c>
       <c r="R29" t="n">
-        <v>6417475</v>
+        <v>6417518</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3777,7 +3635,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3796,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460916</v>
+        <v>122460731</v>
       </c>
       <c r="B30" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3813,11 +3670,6 @@
       </c>
       <c r="E30" t="n">
         <v>220787</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3844,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566783</v>
+        <v>566693</v>
       </c>
       <c r="R30" t="n">
-        <v>6417513</v>
+        <v>6417493</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460572</v>
+        <v>122460769</v>
       </c>
       <c r="B31" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3924,11 +3776,6 @@
       </c>
       <c r="E31" t="n">
         <v>220787</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3955,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566746</v>
+        <v>566727</v>
       </c>
       <c r="R31" t="n">
-        <v>6417537</v>
+        <v>6417559</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460794</v>
+        <v>122460400</v>
       </c>
       <c r="B32" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4035,11 +3882,6 @@
       </c>
       <c r="E32" t="n">
         <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4066,10 +3908,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566775</v>
+        <v>566747</v>
       </c>
       <c r="R32" t="n">
-        <v>6417541</v>
+        <v>6417470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,10 +3971,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460353</v>
+        <v>122460743</v>
       </c>
       <c r="B33" t="n">
-        <v>98202</v>
+        <v>91216</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4141,35 +3983,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5420</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4177,10 +4017,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566758</v>
+        <v>566698</v>
       </c>
       <c r="R33" t="n">
-        <v>6417479</v>
+        <v>6417489</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,10 +4080,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460786</v>
+        <v>122460919</v>
       </c>
       <c r="B34" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4257,11 +4097,6 @@
       </c>
       <c r="E34" t="n">
         <v>220787</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4288,10 +4123,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566755</v>
+        <v>566772</v>
       </c>
       <c r="R34" t="n">
-        <v>6417553</v>
+        <v>6417498</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460440</v>
+        <v>122460839</v>
       </c>
       <c r="B9" t="n">
         <v>98211</v>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566775</v>
+        <v>566801</v>
       </c>
       <c r="R9" t="n">
-        <v>6417497</v>
+        <v>6417510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460839</v>
+        <v>122460440</v>
       </c>
       <c r="B10" t="n">
         <v>98211</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566801</v>
+        <v>566775</v>
       </c>
       <c r="R10" t="n">
-        <v>6417510</v>
+        <v>6417497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460916</v>
+        <v>122460934</v>
       </c>
       <c r="B26" t="n">
-        <v>98211</v>
+        <v>57749</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,30 +3238,34 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3269,13 +3273,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566783</v>
+        <v>566622</v>
       </c>
       <c r="R26" t="n">
-        <v>6417513</v>
+        <v>6417518</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3313,7 +3317,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3332,7 +3335,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460760</v>
+        <v>122460916</v>
       </c>
       <c r="B27" t="n">
         <v>98211</v>
@@ -3375,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566688</v>
+        <v>566783</v>
       </c>
       <c r="R27" t="n">
-        <v>6417511</v>
+        <v>6417513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3438,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460491</v>
+        <v>122460760</v>
       </c>
       <c r="B28" t="n">
         <v>98211</v>
@@ -3481,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566757</v>
+        <v>566688</v>
       </c>
       <c r="R28" t="n">
-        <v>6417517</v>
+        <v>6417511</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3544,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460934</v>
+        <v>122460491</v>
       </c>
       <c r="B29" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3556,34 +3559,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3591,13 +3590,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566622</v>
+        <v>566757</v>
       </c>
       <c r="R29" t="n">
-        <v>6417518</v>
+        <v>6417517</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3635,6 +3634,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460353</v>
+        <v>122460743</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>91229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566758</v>
+        <v>566698</v>
       </c>
       <c r="R2" t="n">
-        <v>6417479</v>
+        <v>6417489</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460363</v>
+        <v>122460830</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,6 +806,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -824,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566758</v>
+        <v>566776</v>
       </c>
       <c r="R3" t="n">
-        <v>6417476</v>
+        <v>6417537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460754</v>
+        <v>122460786</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,6 +917,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -930,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566688</v>
+        <v>566755</v>
       </c>
       <c r="R4" t="n">
-        <v>6417499</v>
+        <v>6417553</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460509</v>
+        <v>122460434</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,6 +1028,11 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1036,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566762</v>
+        <v>566795</v>
       </c>
       <c r="R5" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460716</v>
+        <v>122460478</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,6 +1139,11 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1142,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566691</v>
+        <v>566761</v>
       </c>
       <c r="R6" t="n">
-        <v>6417494</v>
+        <v>6417508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460478</v>
+        <v>122460919</v>
       </c>
       <c r="B7" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,6 +1250,11 @@
       </c>
       <c r="E7" t="n">
         <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1248,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566761</v>
+        <v>566772</v>
       </c>
       <c r="R7" t="n">
-        <v>6417508</v>
+        <v>6417498</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460581</v>
+        <v>122460522</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,6 +1362,11 @@
       <c r="E8" t="n">
         <v>220787</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1345,7 +1383,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1354,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566740</v>
+        <v>566762</v>
       </c>
       <c r="R8" t="n">
-        <v>6417531</v>
+        <v>6417537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460839</v>
+        <v>122460411</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,6 +1476,11 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1460,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566801</v>
+        <v>566756</v>
       </c>
       <c r="R9" t="n">
-        <v>6417510</v>
+        <v>6417478</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460440</v>
+        <v>122460558</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,6 +1587,11 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1566,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566775</v>
+        <v>566735</v>
       </c>
       <c r="R10" t="n">
-        <v>6417497</v>
+        <v>6417522</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460411</v>
+        <v>122460363</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,6 +1698,11 @@
       </c>
       <c r="E11" t="n">
         <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1672,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566756</v>
+        <v>566758</v>
       </c>
       <c r="R11" t="n">
-        <v>6417478</v>
+        <v>6417476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460450</v>
+        <v>122460420</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,6 +1809,11 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1778,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566761</v>
+        <v>566778</v>
       </c>
       <c r="R12" t="n">
-        <v>6417502</v>
+        <v>6417475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460830</v>
+        <v>122460794</v>
       </c>
       <c r="B13" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,6 +1920,11 @@
       </c>
       <c r="E13" t="n">
         <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1884,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566776</v>
+        <v>566775</v>
       </c>
       <c r="R13" t="n">
-        <v>6417537</v>
+        <v>6417541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460572</v>
+        <v>122460462</v>
       </c>
       <c r="B14" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,6 +2031,11 @@
       </c>
       <c r="E14" t="n">
         <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1990,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566746</v>
+        <v>566759</v>
       </c>
       <c r="R14" t="n">
-        <v>6417537</v>
+        <v>6417510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460794</v>
+        <v>122460929</v>
       </c>
       <c r="B15" t="n">
-        <v>98211</v>
+        <v>57536</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,30 +2137,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2096,13 +2177,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566775</v>
+        <v>566622</v>
       </c>
       <c r="R15" t="n">
-        <v>6417541</v>
+        <v>6417518</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2140,7 +2221,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2159,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460786</v>
+        <v>122460427</v>
       </c>
       <c r="B16" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,6 +2256,11 @@
       </c>
       <c r="E16" t="n">
         <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2202,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566755</v>
+        <v>566763</v>
       </c>
       <c r="R16" t="n">
-        <v>6417553</v>
+        <v>6417499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460558</v>
+        <v>122460731</v>
       </c>
       <c r="B17" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,6 +2367,11 @@
       </c>
       <c r="E17" t="n">
         <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2308,10 +2398,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566735</v>
+        <v>566693</v>
       </c>
       <c r="R17" t="n">
-        <v>6417522</v>
+        <v>6417493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460929</v>
+        <v>122460727</v>
       </c>
       <c r="B18" t="n">
-        <v>57532</v>
+        <v>98224</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,34 +2473,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2418,13 +2509,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566622</v>
+        <v>566693</v>
       </c>
       <c r="R18" t="n">
-        <v>6417518</v>
+        <v>6417494</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2462,6 +2553,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2480,10 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460310</v>
+        <v>122460450</v>
       </c>
       <c r="B19" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,6 +2590,11 @@
       <c r="E19" t="n">
         <v>220787</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -2514,11 +2611,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2527,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566794</v>
+        <v>566761</v>
       </c>
       <c r="R19" t="n">
-        <v>6417463</v>
+        <v>6417502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460427</v>
+        <v>122460839</v>
       </c>
       <c r="B20" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,6 +2700,11 @@
       </c>
       <c r="E20" t="n">
         <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2633,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566763</v>
+        <v>566801</v>
       </c>
       <c r="R20" t="n">
-        <v>6417499</v>
+        <v>6417510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460462</v>
+        <v>122460754</v>
       </c>
       <c r="B21" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,6 +2811,11 @@
       </c>
       <c r="E21" t="n">
         <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2739,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566759</v>
+        <v>566688</v>
       </c>
       <c r="R21" t="n">
-        <v>6417510</v>
+        <v>6417499</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2802,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460344</v>
+        <v>122460400</v>
       </c>
       <c r="B22" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,6 +2922,11 @@
       </c>
       <c r="E22" t="n">
         <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2845,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566761</v>
+        <v>566747</v>
       </c>
       <c r="R22" t="n">
-        <v>6417474</v>
+        <v>6417470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2908,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460727</v>
+        <v>122460769</v>
       </c>
       <c r="B23" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,6 +3033,11 @@
       </c>
       <c r="E23" t="n">
         <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2951,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566693</v>
+        <v>566727</v>
       </c>
       <c r="R23" t="n">
-        <v>6417494</v>
+        <v>6417559</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460434</v>
+        <v>122460440</v>
       </c>
       <c r="B24" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,6 +3144,11 @@
       </c>
       <c r="E24" t="n">
         <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -3057,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566795</v>
+        <v>566775</v>
       </c>
       <c r="R24" t="n">
-        <v>6417518</v>
+        <v>6417497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460420</v>
+        <v>122460916</v>
       </c>
       <c r="B25" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,6 +3255,11 @@
       </c>
       <c r="E25" t="n">
         <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3163,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566778</v>
+        <v>566783</v>
       </c>
       <c r="R25" t="n">
-        <v>6417475</v>
+        <v>6417513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460934</v>
+        <v>122460716</v>
       </c>
       <c r="B26" t="n">
-        <v>57749</v>
+        <v>98224</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,34 +3361,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3273,13 +3397,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566622</v>
+        <v>566691</v>
       </c>
       <c r="R26" t="n">
-        <v>6417518</v>
+        <v>6417494</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3317,6 +3441,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3335,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460916</v>
+        <v>122460310</v>
       </c>
       <c r="B27" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3353,6 +3478,11 @@
       <c r="E27" t="n">
         <v>220787</v>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -3369,7 +3499,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3378,10 +3512,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566783</v>
+        <v>566794</v>
       </c>
       <c r="R27" t="n">
-        <v>6417513</v>
+        <v>6417463</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,10 +3575,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460760</v>
+        <v>122460353</v>
       </c>
       <c r="B28" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3458,6 +3592,11 @@
       </c>
       <c r="E28" t="n">
         <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3484,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566688</v>
+        <v>566758</v>
       </c>
       <c r="R28" t="n">
-        <v>6417511</v>
+        <v>6417479</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3547,10 +3686,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460491</v>
+        <v>122460760</v>
       </c>
       <c r="B29" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,6 +3703,11 @@
       </c>
       <c r="E29" t="n">
         <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3590,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566757</v>
+        <v>566688</v>
       </c>
       <c r="R29" t="n">
-        <v>6417517</v>
+        <v>6417511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3653,10 +3797,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460731</v>
+        <v>122460572</v>
       </c>
       <c r="B30" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,6 +3814,11 @@
       </c>
       <c r="E30" t="n">
         <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3696,10 +3845,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566693</v>
+        <v>566746</v>
       </c>
       <c r="R30" t="n">
-        <v>6417493</v>
+        <v>6417537</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3759,10 +3908,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460769</v>
+        <v>122460344</v>
       </c>
       <c r="B31" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3776,6 +3925,11 @@
       </c>
       <c r="E31" t="n">
         <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3802,10 +3956,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566727</v>
+        <v>566761</v>
       </c>
       <c r="R31" t="n">
-        <v>6417559</v>
+        <v>6417474</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3865,10 +4019,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460400</v>
+        <v>122460581</v>
       </c>
       <c r="B32" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3882,6 +4036,11 @@
       </c>
       <c r="E32" t="n">
         <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3908,10 +4067,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566747</v>
+        <v>566740</v>
       </c>
       <c r="R32" t="n">
-        <v>6417470</v>
+        <v>6417531</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3971,10 +4130,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460743</v>
+        <v>122460491</v>
       </c>
       <c r="B33" t="n">
-        <v>91216</v>
+        <v>98224</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,33 +4142,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5420</v>
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4017,10 +4178,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566698</v>
+        <v>566757</v>
       </c>
       <c r="R33" t="n">
-        <v>6417489</v>
+        <v>6417517</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4080,10 +4241,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460919</v>
+        <v>122460934</v>
       </c>
       <c r="B34" t="n">
-        <v>98211</v>
+        <v>57753</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4092,30 +4253,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103015</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4123,13 +4293,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566772</v>
+        <v>566622</v>
       </c>
       <c r="R34" t="n">
-        <v>6417498</v>
+        <v>6417518</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4167,7 +4337,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460743</v>
+        <v>122460581</v>
       </c>
       <c r="B2" t="n">
-        <v>91229</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566698</v>
+        <v>566740</v>
       </c>
       <c r="R2" t="n">
-        <v>6417489</v>
+        <v>6417531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460830</v>
+        <v>122460509</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,7 +834,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566776</v>
+        <v>566762</v>
       </c>
       <c r="R3" t="n">
         <v>6417537</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460786</v>
+        <v>122460462</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566755</v>
+        <v>566759</v>
       </c>
       <c r="R4" t="n">
-        <v>6417553</v>
+        <v>6417510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460434</v>
+        <v>122460727</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566795</v>
+        <v>566693</v>
       </c>
       <c r="R5" t="n">
-        <v>6417518</v>
+        <v>6417494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460478</v>
+        <v>122460919</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566761</v>
+        <v>566772</v>
       </c>
       <c r="R6" t="n">
-        <v>6417508</v>
+        <v>6417498</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460919</v>
+        <v>122460427</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566772</v>
+        <v>566763</v>
       </c>
       <c r="R7" t="n">
-        <v>6417498</v>
+        <v>6417499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460522</v>
+        <v>122460929</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>57536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1353,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566762</v>
+        <v>566622</v>
       </c>
       <c r="R8" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1437,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1459,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460411</v>
+        <v>122460769</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566756</v>
+        <v>566727</v>
       </c>
       <c r="R9" t="n">
-        <v>6417478</v>
+        <v>6417559</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460558</v>
+        <v>122460916</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566735</v>
+        <v>566783</v>
       </c>
       <c r="R10" t="n">
-        <v>6417522</v>
+        <v>6417513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460363</v>
+        <v>122460411</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566758</v>
+        <v>566756</v>
       </c>
       <c r="R11" t="n">
-        <v>6417476</v>
+        <v>6417478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460420</v>
+        <v>122460434</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566778</v>
+        <v>566795</v>
       </c>
       <c r="R12" t="n">
-        <v>6417475</v>
+        <v>6417518</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460794</v>
+        <v>122460310</v>
       </c>
       <c r="B13" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,7 +1938,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566775</v>
+        <v>566794</v>
       </c>
       <c r="R13" t="n">
-        <v>6417541</v>
+        <v>6417463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460462</v>
+        <v>122460363</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566759</v>
+        <v>566758</v>
       </c>
       <c r="R14" t="n">
-        <v>6417510</v>
+        <v>6417476</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460929</v>
+        <v>122460478</v>
       </c>
       <c r="B15" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,39 +2137,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2177,13 +2173,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566622</v>
+        <v>566761</v>
       </c>
       <c r="R15" t="n">
-        <v>6417518</v>
+        <v>6417508</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,6 +2217,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460427</v>
+        <v>122460450</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R16" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460731</v>
+        <v>122460440</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566693</v>
+        <v>566775</v>
       </c>
       <c r="R17" t="n">
-        <v>6417493</v>
+        <v>6417497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460727</v>
+        <v>122460806</v>
       </c>
       <c r="B18" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566693</v>
+        <v>566775</v>
       </c>
       <c r="R18" t="n">
-        <v>6417494</v>
+        <v>6417541</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460450</v>
+        <v>122460731</v>
       </c>
       <c r="B19" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566761</v>
+        <v>566693</v>
       </c>
       <c r="R19" t="n">
-        <v>6417502</v>
+        <v>6417493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460839</v>
+        <v>122460934</v>
       </c>
       <c r="B20" t="n">
-        <v>98224</v>
+        <v>57753</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2695,35 +2692,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2731,13 +2732,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566801</v>
+        <v>566622</v>
       </c>
       <c r="R20" t="n">
-        <v>6417510</v>
+        <v>6417518</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2775,7 +2776,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460754</v>
+        <v>122460760</v>
       </c>
       <c r="B21" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>566688</v>
       </c>
       <c r="R21" t="n">
-        <v>6417499</v>
+        <v>6417511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460400</v>
+        <v>122460839</v>
       </c>
       <c r="B22" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566747</v>
+        <v>566801</v>
       </c>
       <c r="R22" t="n">
-        <v>6417470</v>
+        <v>6417510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460769</v>
+        <v>122460716</v>
       </c>
       <c r="B23" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566727</v>
+        <v>566691</v>
       </c>
       <c r="R23" t="n">
-        <v>6417559</v>
+        <v>6417494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460440</v>
+        <v>122460754</v>
       </c>
       <c r="B24" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566775</v>
+        <v>566688</v>
       </c>
       <c r="R24" t="n">
-        <v>6417497</v>
+        <v>6417499</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460916</v>
+        <v>122460344</v>
       </c>
       <c r="B25" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566783</v>
+        <v>566761</v>
       </c>
       <c r="R25" t="n">
-        <v>6417513</v>
+        <v>6417474</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,10 +3349,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460716</v>
+        <v>122460786</v>
       </c>
       <c r="B26" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566691</v>
+        <v>566755</v>
       </c>
       <c r="R26" t="n">
-        <v>6417494</v>
+        <v>6417553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460310</v>
+        <v>122460572</v>
       </c>
       <c r="B27" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3499,11 +3499,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3512,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566794</v>
+        <v>566746</v>
       </c>
       <c r="R27" t="n">
-        <v>6417463</v>
+        <v>6417537</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3575,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460353</v>
+        <v>122460558</v>
       </c>
       <c r="B28" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3623,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566758</v>
+        <v>566735</v>
       </c>
       <c r="R28" t="n">
-        <v>6417479</v>
+        <v>6417522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460760</v>
+        <v>122460400</v>
       </c>
       <c r="B29" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3734,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566688</v>
+        <v>566747</v>
       </c>
       <c r="R29" t="n">
-        <v>6417511</v>
+        <v>6417470</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3797,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460572</v>
+        <v>122460743</v>
       </c>
       <c r="B30" t="n">
-        <v>98224</v>
+        <v>91242</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3809,35 +3805,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3845,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566746</v>
+        <v>566698</v>
       </c>
       <c r="R30" t="n">
-        <v>6417537</v>
+        <v>6417489</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,10 +3907,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460344</v>
+        <v>122460830</v>
       </c>
       <c r="B31" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3956,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566761</v>
+        <v>566776</v>
       </c>
       <c r="R31" t="n">
-        <v>6417474</v>
+        <v>6417537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4019,10 +4018,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460581</v>
+        <v>122460353</v>
       </c>
       <c r="B32" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,10 +4066,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566740</v>
+        <v>566758</v>
       </c>
       <c r="R32" t="n">
-        <v>6417531</v>
+        <v>6417479</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4130,10 +4129,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460491</v>
+        <v>122460420</v>
       </c>
       <c r="B33" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4178,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566757</v>
+        <v>566778</v>
       </c>
       <c r="R33" t="n">
-        <v>6417517</v>
+        <v>6417475</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460934</v>
+        <v>122460491</v>
       </c>
       <c r="B34" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4253,39 +4252,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4293,13 +4288,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566622</v>
+        <v>566757</v>
       </c>
       <c r="R34" t="n">
-        <v>6417518</v>
+        <v>6417517</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4337,6 +4332,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460581</v>
+        <v>122460572</v>
       </c>
       <c r="B2" t="n">
         <v>98237</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566740</v>
+        <v>566746</v>
       </c>
       <c r="R2" t="n">
-        <v>6417531</v>
+        <v>6417537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460509</v>
+        <v>122460545</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460462</v>
+        <v>122460754</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566759</v>
+        <v>566688</v>
       </c>
       <c r="R4" t="n">
-        <v>6417510</v>
+        <v>6417499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460727</v>
+        <v>122460491</v>
       </c>
       <c r="B5" t="n">
         <v>98237</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566693</v>
+        <v>566757</v>
       </c>
       <c r="R5" t="n">
-        <v>6417494</v>
+        <v>6417517</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460919</v>
+        <v>122460934</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566772</v>
+        <v>566622</v>
       </c>
       <c r="R6" t="n">
-        <v>6417498</v>
+        <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460427</v>
+        <v>122460450</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R7" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460929</v>
+        <v>122460420</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566622</v>
+        <v>566778</v>
       </c>
       <c r="R8" t="n">
-        <v>6417518</v>
+        <v>6417475</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1436,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460769</v>
+        <v>122460786</v>
       </c>
       <c r="B9" t="n">
         <v>98237</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566727</v>
+        <v>566755</v>
       </c>
       <c r="R9" t="n">
-        <v>6417559</v>
+        <v>6417553</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460916</v>
+        <v>122460727</v>
       </c>
       <c r="B10" t="n">
         <v>98237</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566783</v>
+        <v>566693</v>
       </c>
       <c r="R10" t="n">
-        <v>6417513</v>
+        <v>6417494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460411</v>
+        <v>122460769</v>
       </c>
       <c r="B11" t="n">
         <v>98237</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566756</v>
+        <v>566727</v>
       </c>
       <c r="R11" t="n">
-        <v>6417478</v>
+        <v>6417559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460434</v>
+        <v>122460400</v>
       </c>
       <c r="B12" t="n">
         <v>98237</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566795</v>
+        <v>566747</v>
       </c>
       <c r="R12" t="n">
-        <v>6417518</v>
+        <v>6417470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460310</v>
+        <v>122460363</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -1938,11 +1938,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566794</v>
+        <v>566758</v>
       </c>
       <c r="R13" t="n">
-        <v>6417463</v>
+        <v>6417476</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460363</v>
+        <v>122460839</v>
       </c>
       <c r="B14" t="n">
         <v>98237</v>
@@ -2062,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566758</v>
+        <v>566801</v>
       </c>
       <c r="R14" t="n">
-        <v>6417476</v>
+        <v>6417510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460478</v>
+        <v>122460558</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2173,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566761</v>
+        <v>566735</v>
       </c>
       <c r="R15" t="n">
-        <v>6417508</v>
+        <v>6417522</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460450</v>
+        <v>122460916</v>
       </c>
       <c r="B16" t="n">
         <v>98237</v>
@@ -2284,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566761</v>
+        <v>566783</v>
       </c>
       <c r="R16" t="n">
-        <v>6417502</v>
+        <v>6417513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2343,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460440</v>
+        <v>122460462</v>
       </c>
       <c r="B17" t="n">
         <v>98237</v>
@@ -2395,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566775</v>
+        <v>566759</v>
       </c>
       <c r="R17" t="n">
-        <v>6417497</v>
+        <v>6417510</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460806</v>
+        <v>122460353</v>
       </c>
       <c r="B18" t="n">
         <v>98237</v>
@@ -2506,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566775</v>
+        <v>566758</v>
       </c>
       <c r="R18" t="n">
-        <v>6417541</v>
+        <v>6417479</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,7 +2565,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460731</v>
+        <v>122460581</v>
       </c>
       <c r="B19" t="n">
         <v>98237</v>
@@ -2617,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566693</v>
+        <v>566740</v>
       </c>
       <c r="R19" t="n">
-        <v>6417493</v>
+        <v>6417531</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460934</v>
+        <v>122460427</v>
       </c>
       <c r="B20" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,39 +2688,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2732,13 +2724,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566622</v>
+        <v>566763</v>
       </c>
       <c r="R20" t="n">
-        <v>6417518</v>
+        <v>6417499</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2776,6 +2768,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2794,7 +2787,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460760</v>
+        <v>122460434</v>
       </c>
       <c r="B21" t="n">
         <v>98237</v>
@@ -2842,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566688</v>
+        <v>566795</v>
       </c>
       <c r="R21" t="n">
-        <v>6417511</v>
+        <v>6417518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2898,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460839</v>
+        <v>122460806</v>
       </c>
       <c r="B22" t="n">
         <v>98237</v>
@@ -2953,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566801</v>
+        <v>566775</v>
       </c>
       <c r="R22" t="n">
-        <v>6417510</v>
+        <v>6417541</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3009,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460716</v>
+        <v>122460760</v>
       </c>
       <c r="B23" t="n">
         <v>98237</v>
@@ -3064,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566691</v>
+        <v>566688</v>
       </c>
       <c r="R23" t="n">
-        <v>6417494</v>
+        <v>6417511</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460754</v>
+        <v>122460743</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>91242</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3139,35 +3132,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3175,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566688</v>
+        <v>566698</v>
       </c>
       <c r="R24" t="n">
-        <v>6417499</v>
+        <v>6417489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460344</v>
+        <v>122460929</v>
       </c>
       <c r="B25" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3250,35 +3246,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3286,13 +3286,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566761</v>
+        <v>566622</v>
       </c>
       <c r="R25" t="n">
-        <v>6417474</v>
+        <v>6417518</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,7 +3330,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3349,7 +3348,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460786</v>
+        <v>122460478</v>
       </c>
       <c r="B26" t="n">
         <v>98237</v>
@@ -3397,10 +3396,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566755</v>
+        <v>566761</v>
       </c>
       <c r="R26" t="n">
-        <v>6417553</v>
+        <v>6417508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,7 +3459,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460572</v>
+        <v>122460731</v>
       </c>
       <c r="B27" t="n">
         <v>98237</v>
@@ -3508,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566746</v>
+        <v>566693</v>
       </c>
       <c r="R27" t="n">
-        <v>6417537</v>
+        <v>6417493</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,7 +3570,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460558</v>
+        <v>122460310</v>
       </c>
       <c r="B28" t="n">
         <v>98237</v>
@@ -3610,7 +3609,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3619,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566735</v>
+        <v>566794</v>
       </c>
       <c r="R28" t="n">
-        <v>6417522</v>
+        <v>6417463</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,7 +3685,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460400</v>
+        <v>122460830</v>
       </c>
       <c r="B29" t="n">
         <v>98237</v>
@@ -3730,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566747</v>
+        <v>566776</v>
       </c>
       <c r="R29" t="n">
-        <v>6417470</v>
+        <v>6417537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460743</v>
+        <v>122460411</v>
       </c>
       <c r="B30" t="n">
-        <v>91242</v>
+        <v>98237</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3805,38 +3808,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566698</v>
+        <v>566756</v>
       </c>
       <c r="R30" t="n">
-        <v>6417489</v>
+        <v>6417478</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460830</v>
+        <v>122460344</v>
       </c>
       <c r="B31" t="n">
         <v>98237</v>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566776</v>
+        <v>566761</v>
       </c>
       <c r="R31" t="n">
-        <v>6417537</v>
+        <v>6417474</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460353</v>
+        <v>122460919</v>
       </c>
       <c r="B32" t="n">
         <v>98237</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566758</v>
+        <v>566772</v>
       </c>
       <c r="R32" t="n">
-        <v>6417479</v>
+        <v>6417498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460420</v>
+        <v>122460716</v>
       </c>
       <c r="B33" t="n">
         <v>98237</v>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566778</v>
+        <v>566691</v>
       </c>
       <c r="R33" t="n">
-        <v>6417475</v>
+        <v>6417494</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460491</v>
+        <v>122460440</v>
       </c>
       <c r="B34" t="n">
         <v>98237</v>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566757</v>
+        <v>566775</v>
       </c>
       <c r="R34" t="n">
-        <v>6417517</v>
+        <v>6417497</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460754</v>
+        <v>122460491</v>
       </c>
       <c r="B4" t="n">
         <v>98237</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566688</v>
+        <v>566757</v>
       </c>
       <c r="R4" t="n">
-        <v>6417499</v>
+        <v>6417517</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460491</v>
+        <v>122460754</v>
       </c>
       <c r="B5" t="n">
         <v>98237</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566757</v>
+        <v>566688</v>
       </c>
       <c r="R5" t="n">
-        <v>6417517</v>
+        <v>6417499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460400</v>
+        <v>122460363</v>
       </c>
       <c r="B12" t="n">
         <v>98237</v>
@@ -1836,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566747</v>
+        <v>566758</v>
       </c>
       <c r="R12" t="n">
-        <v>6417470</v>
+        <v>6417476</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460363</v>
+        <v>122460839</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566758</v>
+        <v>566801</v>
       </c>
       <c r="R13" t="n">
-        <v>6417476</v>
+        <v>6417510</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460839</v>
+        <v>122460400</v>
       </c>
       <c r="B14" t="n">
         <v>98237</v>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566801</v>
+        <v>566747</v>
       </c>
       <c r="R14" t="n">
-        <v>6417510</v>
+        <v>6417470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460572</v>
+        <v>122460929</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566746</v>
+        <v>566622</v>
       </c>
       <c r="R2" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460545</v>
+        <v>122460411</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566762</v>
+        <v>566756</v>
       </c>
       <c r="R3" t="n">
-        <v>6417537</v>
+        <v>6417478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460491</v>
+        <v>122460344</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566757</v>
+        <v>566761</v>
       </c>
       <c r="R4" t="n">
-        <v>6417517</v>
+        <v>6417474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460754</v>
+        <v>122460830</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566688</v>
+        <v>566776</v>
       </c>
       <c r="R5" t="n">
-        <v>6417499</v>
+        <v>6417537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460934</v>
+        <v>122460353</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566622</v>
+        <v>566758</v>
       </c>
       <c r="R6" t="n">
-        <v>6417518</v>
+        <v>6417479</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460450</v>
+        <v>122460839</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566761</v>
+        <v>566801</v>
       </c>
       <c r="R7" t="n">
-        <v>6417502</v>
+        <v>6417510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460420</v>
+        <v>122460450</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566778</v>
+        <v>566761</v>
       </c>
       <c r="R8" t="n">
-        <v>6417475</v>
+        <v>6417502</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460786</v>
+        <v>122460572</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566755</v>
+        <v>566746</v>
       </c>
       <c r="R9" t="n">
-        <v>6417553</v>
+        <v>6417537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460727</v>
+        <v>122460427</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566693</v>
+        <v>566763</v>
       </c>
       <c r="R10" t="n">
-        <v>6417494</v>
+        <v>6417499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460769</v>
+        <v>122460581</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566727</v>
+        <v>566740</v>
       </c>
       <c r="R11" t="n">
-        <v>6417559</v>
+        <v>6417531</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460363</v>
+        <v>122460310</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,7 +1827,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1836,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566758</v>
+        <v>566794</v>
       </c>
       <c r="R12" t="n">
-        <v>6417476</v>
+        <v>6417463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460839</v>
+        <v>122460727</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566801</v>
+        <v>566693</v>
       </c>
       <c r="R13" t="n">
-        <v>6417510</v>
+        <v>6417494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460400</v>
+        <v>122460440</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566747</v>
+        <v>566775</v>
       </c>
       <c r="R14" t="n">
-        <v>6417470</v>
+        <v>6417497</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460558</v>
+        <v>122460919</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566735</v>
+        <v>566772</v>
       </c>
       <c r="R15" t="n">
-        <v>6417522</v>
+        <v>6417498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460916</v>
+        <v>122460478</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566783</v>
+        <v>566761</v>
       </c>
       <c r="R16" t="n">
-        <v>6417513</v>
+        <v>6417508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460462</v>
+        <v>122460400</v>
       </c>
       <c r="B17" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566759</v>
+        <v>566747</v>
       </c>
       <c r="R17" t="n">
-        <v>6417510</v>
+        <v>6417470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460353</v>
+        <v>122460794</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566758</v>
+        <v>566775</v>
       </c>
       <c r="R18" t="n">
-        <v>6417479</v>
+        <v>6417541</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460581</v>
+        <v>122460760</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2613,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566740</v>
+        <v>566688</v>
       </c>
       <c r="R19" t="n">
-        <v>6417531</v>
+        <v>6417511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460427</v>
+        <v>122460786</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2728,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566763</v>
+        <v>566755</v>
       </c>
       <c r="R20" t="n">
-        <v>6417499</v>
+        <v>6417553</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460434</v>
+        <v>122460743</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>91243</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,35 +2803,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2835,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566795</v>
+        <v>566698</v>
       </c>
       <c r="R21" t="n">
-        <v>6417518</v>
+        <v>6417489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460806</v>
+        <v>122460934</v>
       </c>
       <c r="B22" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2910,35 +2917,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2946,13 +2957,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566775</v>
+        <v>566622</v>
       </c>
       <c r="R22" t="n">
-        <v>6417541</v>
+        <v>6417518</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +3001,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3009,10 +3019,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460760</v>
+        <v>122460491</v>
       </c>
       <c r="B23" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566688</v>
+        <v>566757</v>
       </c>
       <c r="R23" t="n">
-        <v>6417511</v>
+        <v>6417517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460743</v>
+        <v>122460731</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>98240</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3132,38 +3142,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3171,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566698</v>
+        <v>566693</v>
       </c>
       <c r="R24" t="n">
-        <v>6417489</v>
+        <v>6417493</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3241,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460929</v>
+        <v>122460545</v>
       </c>
       <c r="B25" t="n">
-        <v>57536</v>
+        <v>98240</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,39 +3253,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3286,13 +3289,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566622</v>
+        <v>566762</v>
       </c>
       <c r="R25" t="n">
-        <v>6417518</v>
+        <v>6417537</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,6 +3333,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3348,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460478</v>
+        <v>122460769</v>
       </c>
       <c r="B26" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3396,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566761</v>
+        <v>566727</v>
       </c>
       <c r="R26" t="n">
-        <v>6417508</v>
+        <v>6417559</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3459,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460731</v>
+        <v>122460462</v>
       </c>
       <c r="B27" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3507,10 +3511,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566693</v>
+        <v>566759</v>
       </c>
       <c r="R27" t="n">
-        <v>6417493</v>
+        <v>6417510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,10 +3574,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460310</v>
+        <v>122460558</v>
       </c>
       <c r="B28" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,11 +3613,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566794</v>
+        <v>566735</v>
       </c>
       <c r="R28" t="n">
-        <v>6417463</v>
+        <v>6417522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,10 +3685,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460830</v>
+        <v>122460716</v>
       </c>
       <c r="B29" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566776</v>
+        <v>566691</v>
       </c>
       <c r="R29" t="n">
-        <v>6417537</v>
+        <v>6417494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460411</v>
+        <v>122460916</v>
       </c>
       <c r="B30" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566756</v>
+        <v>566783</v>
       </c>
       <c r="R30" t="n">
-        <v>6417478</v>
+        <v>6417513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460344</v>
+        <v>122460434</v>
       </c>
       <c r="B31" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566761</v>
+        <v>566795</v>
       </c>
       <c r="R31" t="n">
-        <v>6417474</v>
+        <v>6417518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,10 +4018,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460919</v>
+        <v>122460420</v>
       </c>
       <c r="B32" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566772</v>
+        <v>566778</v>
       </c>
       <c r="R32" t="n">
-        <v>6417498</v>
+        <v>6417475</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460716</v>
+        <v>122460363</v>
       </c>
       <c r="B33" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566691</v>
+        <v>566758</v>
       </c>
       <c r="R33" t="n">
-        <v>6417494</v>
+        <v>6417476</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460440</v>
+        <v>122460754</v>
       </c>
       <c r="B34" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566775</v>
+        <v>566688</v>
       </c>
       <c r="R34" t="n">
-        <v>6417497</v>
+        <v>6417499</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460929</v>
+        <v>122460363</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566622</v>
+        <v>566758</v>
       </c>
       <c r="R2" t="n">
-        <v>6417518</v>
+        <v>6417476</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460411</v>
+        <v>122460344</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566756</v>
+        <v>566761</v>
       </c>
       <c r="R3" t="n">
-        <v>6417478</v>
+        <v>6417474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460344</v>
+        <v>122460522</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -939,7 +936,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566761</v>
+        <v>566762</v>
       </c>
       <c r="R4" t="n">
-        <v>6417474</v>
+        <v>6417537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460830</v>
+        <v>122460839</v>
       </c>
       <c r="B5" t="n">
         <v>98240</v>
@@ -1059,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566776</v>
+        <v>566801</v>
       </c>
       <c r="R5" t="n">
-        <v>6417537</v>
+        <v>6417510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460353</v>
+        <v>122460929</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>57536</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1135,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566758</v>
+        <v>566622</v>
       </c>
       <c r="R6" t="n">
-        <v>6417479</v>
+        <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1219,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,7 +1237,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460839</v>
+        <v>122460830</v>
       </c>
       <c r="B7" t="n">
         <v>98240</v>
@@ -1281,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566801</v>
+        <v>566776</v>
       </c>
       <c r="R7" t="n">
-        <v>6417510</v>
+        <v>6417537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1348,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460450</v>
+        <v>122460769</v>
       </c>
       <c r="B8" t="n">
         <v>98240</v>
@@ -1392,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566761</v>
+        <v>566727</v>
       </c>
       <c r="R8" t="n">
-        <v>6417502</v>
+        <v>6417559</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460572</v>
+        <v>122460427</v>
       </c>
       <c r="B9" t="n">
         <v>98240</v>
@@ -1503,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566746</v>
+        <v>566763</v>
       </c>
       <c r="R9" t="n">
-        <v>6417537</v>
+        <v>6417499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1570,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460427</v>
+        <v>122460919</v>
       </c>
       <c r="B10" t="n">
         <v>98240</v>
@@ -1614,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566763</v>
+        <v>566772</v>
       </c>
       <c r="R10" t="n">
-        <v>6417499</v>
+        <v>6417498</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1681,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460581</v>
+        <v>122460786</v>
       </c>
       <c r="B11" t="n">
         <v>98240</v>
@@ -1725,10 +1729,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566740</v>
+        <v>566755</v>
       </c>
       <c r="R11" t="n">
-        <v>6417531</v>
+        <v>6417553</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460310</v>
+        <v>122460420</v>
       </c>
       <c r="B12" t="n">
         <v>98240</v>
@@ -1827,11 +1831,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566794</v>
+        <v>566778</v>
       </c>
       <c r="R12" t="n">
-        <v>6417463</v>
+        <v>6417475</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460727</v>
+        <v>122460411</v>
       </c>
       <c r="B13" t="n">
         <v>98240</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566693</v>
+        <v>566756</v>
       </c>
       <c r="R13" t="n">
-        <v>6417494</v>
+        <v>6417478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460440</v>
+        <v>122460310</v>
       </c>
       <c r="B14" t="n">
         <v>98240</v>
@@ -2053,7 +2053,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2062,10 +2066,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566775</v>
+        <v>566794</v>
       </c>
       <c r="R14" t="n">
-        <v>6417497</v>
+        <v>6417463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2129,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460919</v>
+        <v>122460581</v>
       </c>
       <c r="B15" t="n">
         <v>98240</v>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566772</v>
+        <v>566740</v>
       </c>
       <c r="R15" t="n">
-        <v>6417498</v>
+        <v>6417531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460478</v>
+        <v>122460462</v>
       </c>
       <c r="B16" t="n">
         <v>98240</v>
@@ -2284,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566761</v>
+        <v>566759</v>
       </c>
       <c r="R16" t="n">
-        <v>6417508</v>
+        <v>6417510</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460400</v>
+        <v>122460934</v>
       </c>
       <c r="B17" t="n">
-        <v>98240</v>
+        <v>57753</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2359,35 +2363,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2395,13 +2403,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566747</v>
+        <v>566622</v>
       </c>
       <c r="R17" t="n">
-        <v>6417470</v>
+        <v>6417518</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2439,7 +2447,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2465,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460794</v>
+        <v>122460478</v>
       </c>
       <c r="B18" t="n">
         <v>98240</v>
@@ -2506,10 +2513,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566775</v>
+        <v>566761</v>
       </c>
       <c r="R18" t="n">
-        <v>6417541</v>
+        <v>6417508</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,7 +2576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460760</v>
+        <v>122460440</v>
       </c>
       <c r="B19" t="n">
         <v>98240</v>
@@ -2617,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566688</v>
+        <v>566775</v>
       </c>
       <c r="R19" t="n">
-        <v>6417511</v>
+        <v>6417497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,7 +2687,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460786</v>
+        <v>122460400</v>
       </c>
       <c r="B20" t="n">
         <v>98240</v>
@@ -2728,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566755</v>
+        <v>566747</v>
       </c>
       <c r="R20" t="n">
-        <v>6417553</v>
+        <v>6417470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2791,10 +2798,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460743</v>
+        <v>122460794</v>
       </c>
       <c r="B21" t="n">
-        <v>91243</v>
+        <v>98240</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,38 +2810,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2842,10 +2846,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566698</v>
+        <v>566775</v>
       </c>
       <c r="R21" t="n">
-        <v>6417489</v>
+        <v>6417541</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460934</v>
+        <v>122460491</v>
       </c>
       <c r="B22" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2917,39 +2921,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566622</v>
+        <v>566757</v>
       </c>
       <c r="R22" t="n">
-        <v>6417518</v>
+        <v>6417517</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,6 +3001,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3019,7 +3020,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460491</v>
+        <v>122460754</v>
       </c>
       <c r="B23" t="n">
         <v>98240</v>
@@ -3067,10 +3068,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566757</v>
+        <v>566688</v>
       </c>
       <c r="R23" t="n">
-        <v>6417517</v>
+        <v>6417499</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3130,7 +3131,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460731</v>
+        <v>122460572</v>
       </c>
       <c r="B24" t="n">
         <v>98240</v>
@@ -3178,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566693</v>
+        <v>566746</v>
       </c>
       <c r="R24" t="n">
-        <v>6417493</v>
+        <v>6417537</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3241,7 +3242,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460545</v>
+        <v>122460731</v>
       </c>
       <c r="B25" t="n">
         <v>98240</v>
@@ -3289,10 +3290,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566762</v>
+        <v>566693</v>
       </c>
       <c r="R25" t="n">
-        <v>6417537</v>
+        <v>6417493</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3352,10 +3353,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460769</v>
+        <v>122460743</v>
       </c>
       <c r="B26" t="n">
-        <v>98240</v>
+        <v>91243</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,35 +3365,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3400,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566727</v>
+        <v>566698</v>
       </c>
       <c r="R26" t="n">
-        <v>6417559</v>
+        <v>6417489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3467,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460462</v>
+        <v>122460727</v>
       </c>
       <c r="B27" t="n">
         <v>98240</v>
@@ -3511,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566759</v>
+        <v>566693</v>
       </c>
       <c r="R27" t="n">
-        <v>6417510</v>
+        <v>6417494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,7 +3578,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460558</v>
+        <v>122460916</v>
       </c>
       <c r="B28" t="n">
         <v>98240</v>
@@ -3622,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566735</v>
+        <v>566783</v>
       </c>
       <c r="R28" t="n">
-        <v>6417522</v>
+        <v>6417513</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3685,7 +3689,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460716</v>
+        <v>122460450</v>
       </c>
       <c r="B29" t="n">
         <v>98240</v>
@@ -3733,10 +3737,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566691</v>
+        <v>566761</v>
       </c>
       <c r="R29" t="n">
-        <v>6417494</v>
+        <v>6417502</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,7 +3800,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460916</v>
+        <v>122460716</v>
       </c>
       <c r="B30" t="n">
         <v>98240</v>
@@ -3844,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566783</v>
+        <v>566691</v>
       </c>
       <c r="R30" t="n">
-        <v>6417513</v>
+        <v>6417494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4018,7 +4022,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460420</v>
+        <v>122460760</v>
       </c>
       <c r="B32" t="n">
         <v>98240</v>
@@ -4066,10 +4070,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566778</v>
+        <v>566688</v>
       </c>
       <c r="R32" t="n">
-        <v>6417475</v>
+        <v>6417511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,7 +4133,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460363</v>
+        <v>122460558</v>
       </c>
       <c r="B33" t="n">
         <v>98240</v>
@@ -4177,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566758</v>
+        <v>566735</v>
       </c>
       <c r="R33" t="n">
-        <v>6417476</v>
+        <v>6417522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,7 +4244,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460754</v>
+        <v>122460353</v>
       </c>
       <c r="B34" t="n">
         <v>98240</v>
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566688</v>
+        <v>566758</v>
       </c>
       <c r="R34" t="n">
-        <v>6417499</v>
+        <v>6417479</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460363</v>
+        <v>122460839</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566758</v>
+        <v>566801</v>
       </c>
       <c r="R2" t="n">
-        <v>6417476</v>
+        <v>6417510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460344</v>
+        <v>122460434</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566761</v>
+        <v>566795</v>
       </c>
       <c r="R3" t="n">
-        <v>6417474</v>
+        <v>6417518</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460522</v>
+        <v>122460830</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,11 +936,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -949,7 +945,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566762</v>
+        <v>566776</v>
       </c>
       <c r="R4" t="n">
         <v>6417537</v>
@@ -1012,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460839</v>
+        <v>122460509</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566801</v>
+        <v>566762</v>
       </c>
       <c r="R5" t="n">
-        <v>6417510</v>
+        <v>6417537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460929</v>
+        <v>122460769</v>
       </c>
       <c r="B6" t="n">
-        <v>57536</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,39 +1131,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566622</v>
+        <v>566727</v>
       </c>
       <c r="R6" t="n">
-        <v>6417518</v>
+        <v>6417559</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1237,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460830</v>
+        <v>122460353</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566776</v>
+        <v>566758</v>
       </c>
       <c r="R7" t="n">
-        <v>6417537</v>
+        <v>6417479</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460769</v>
+        <v>122460344</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1396,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566727</v>
+        <v>566761</v>
       </c>
       <c r="R8" t="n">
-        <v>6417559</v>
+        <v>6417474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460427</v>
+        <v>122460478</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1507,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R9" t="n">
-        <v>6417499</v>
+        <v>6417508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460919</v>
+        <v>122460462</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566772</v>
+        <v>566759</v>
       </c>
       <c r="R10" t="n">
-        <v>6417498</v>
+        <v>6417510</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460786</v>
+        <v>122460794</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,10 +1722,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566755</v>
+        <v>566775</v>
       </c>
       <c r="R11" t="n">
-        <v>6417553</v>
+        <v>6417541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460420</v>
+        <v>122460411</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1833,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566778</v>
+        <v>566756</v>
       </c>
       <c r="R12" t="n">
-        <v>6417475</v>
+        <v>6417478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460411</v>
+        <v>122460420</v>
       </c>
       <c r="B13" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566756</v>
+        <v>566778</v>
       </c>
       <c r="R13" t="n">
-        <v>6417478</v>
+        <v>6417475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460310</v>
+        <v>122460572</v>
       </c>
       <c r="B14" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,11 +2046,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2066,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566794</v>
+        <v>566746</v>
       </c>
       <c r="R14" t="n">
-        <v>6417463</v>
+        <v>6417537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460581</v>
+        <v>122460934</v>
       </c>
       <c r="B15" t="n">
-        <v>98240</v>
+        <v>57754</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,35 +2130,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2177,13 +2170,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566740</v>
+        <v>566622</v>
       </c>
       <c r="R15" t="n">
-        <v>6417531</v>
+        <v>6417518</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2221,7 +2214,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460462</v>
+        <v>122460363</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,10 +2280,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566759</v>
+        <v>566758</v>
       </c>
       <c r="R16" t="n">
-        <v>6417510</v>
+        <v>6417476</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,10 +2343,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460934</v>
+        <v>122460427</v>
       </c>
       <c r="B17" t="n">
-        <v>57753</v>
+        <v>98241</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,39 +2355,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2403,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566622</v>
+        <v>566763</v>
       </c>
       <c r="R17" t="n">
-        <v>6417518</v>
+        <v>6417499</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,6 +2435,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2465,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460478</v>
+        <v>122460440</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2513,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566761</v>
+        <v>566775</v>
       </c>
       <c r="R18" t="n">
-        <v>6417508</v>
+        <v>6417497</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460440</v>
+        <v>122460400</v>
       </c>
       <c r="B19" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566775</v>
+        <v>566747</v>
       </c>
       <c r="R19" t="n">
-        <v>6417497</v>
+        <v>6417470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460400</v>
+        <v>122460760</v>
       </c>
       <c r="B20" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2735,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566747</v>
+        <v>566688</v>
       </c>
       <c r="R20" t="n">
-        <v>6417470</v>
+        <v>6417511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460794</v>
+        <v>122460558</v>
       </c>
       <c r="B21" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2846,10 +2835,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566775</v>
+        <v>566735</v>
       </c>
       <c r="R21" t="n">
-        <v>6417541</v>
+        <v>6417522</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,10 +2898,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460491</v>
+        <v>122460581</v>
       </c>
       <c r="B22" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2957,10 +2946,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566757</v>
+        <v>566740</v>
       </c>
       <c r="R22" t="n">
-        <v>6417517</v>
+        <v>6417531</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3020,10 +3009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460754</v>
+        <v>122460450</v>
       </c>
       <c r="B23" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3068,10 +3057,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566688</v>
+        <v>566761</v>
       </c>
       <c r="R23" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3131,10 +3120,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460572</v>
+        <v>122460786</v>
       </c>
       <c r="B24" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3179,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566746</v>
+        <v>566755</v>
       </c>
       <c r="R24" t="n">
-        <v>6417537</v>
+        <v>6417553</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3242,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460731</v>
+        <v>122460929</v>
       </c>
       <c r="B25" t="n">
-        <v>98240</v>
+        <v>57537</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3254,35 +3243,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3290,13 +3283,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566693</v>
+        <v>566622</v>
       </c>
       <c r="R25" t="n">
-        <v>6417493</v>
+        <v>6417518</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,7 +3327,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3353,10 +3345,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460743</v>
+        <v>122460491</v>
       </c>
       <c r="B26" t="n">
-        <v>91243</v>
+        <v>98241</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3365,38 +3357,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3404,10 +3393,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566698</v>
+        <v>566757</v>
       </c>
       <c r="R26" t="n">
-        <v>6417489</v>
+        <v>6417517</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3467,10 +3456,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460727</v>
+        <v>122460743</v>
       </c>
       <c r="B27" t="n">
-        <v>98240</v>
+        <v>91244</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3479,35 +3468,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3515,10 +3507,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566693</v>
+        <v>566698</v>
       </c>
       <c r="R27" t="n">
-        <v>6417494</v>
+        <v>6417489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3581,7 +3573,7 @@
         <v>122460916</v>
       </c>
       <c r="B28" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,10 +3681,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460450</v>
+        <v>122460716</v>
       </c>
       <c r="B29" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566761</v>
+        <v>566691</v>
       </c>
       <c r="R29" t="n">
-        <v>6417502</v>
+        <v>6417494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,10 +3792,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460716</v>
+        <v>122460310</v>
       </c>
       <c r="B30" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,7 +3831,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3848,10 +3844,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566691</v>
+        <v>566794</v>
       </c>
       <c r="R30" t="n">
-        <v>6417494</v>
+        <v>6417463</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,10 +3907,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460434</v>
+        <v>122460919</v>
       </c>
       <c r="B31" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566795</v>
+        <v>566772</v>
       </c>
       <c r="R31" t="n">
-        <v>6417518</v>
+        <v>6417498</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,10 +4018,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460760</v>
+        <v>122460727</v>
       </c>
       <c r="B32" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,10 +4066,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566688</v>
+        <v>566693</v>
       </c>
       <c r="R32" t="n">
-        <v>6417511</v>
+        <v>6417494</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4133,10 +4129,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460558</v>
+        <v>122460731</v>
       </c>
       <c r="B33" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566735</v>
+        <v>566693</v>
       </c>
       <c r="R33" t="n">
-        <v>6417522</v>
+        <v>6417493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,10 +4240,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460353</v>
+        <v>122460754</v>
       </c>
       <c r="B34" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566758</v>
+        <v>566688</v>
       </c>
       <c r="R34" t="n">
-        <v>6417479</v>
+        <v>6417499</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460572</v>
+        <v>122460934</v>
       </c>
       <c r="B14" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,35 +2019,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2055,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566746</v>
+        <v>566622</v>
       </c>
       <c r="R14" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2099,7 +2103,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2118,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460934</v>
+        <v>122460572</v>
       </c>
       <c r="B15" t="n">
-        <v>57754</v>
+        <v>98241</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,39 +2133,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2170,13 +2169,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566622</v>
+        <v>566746</v>
       </c>
       <c r="R15" t="n">
-        <v>6417518</v>
+        <v>6417537</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2214,6 +2213,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460839</v>
+        <v>122460934</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566801</v>
+        <v>566622</v>
       </c>
       <c r="R2" t="n">
-        <v>6417510</v>
+        <v>6417518</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460434</v>
+        <v>122460754</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566795</v>
+        <v>566688</v>
       </c>
       <c r="R3" t="n">
-        <v>6417518</v>
+        <v>6417499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460830</v>
+        <v>122460411</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566776</v>
+        <v>566756</v>
       </c>
       <c r="R4" t="n">
-        <v>6417537</v>
+        <v>6417478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460509</v>
+        <v>122460462</v>
       </c>
       <c r="B5" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566762</v>
+        <v>566759</v>
       </c>
       <c r="R5" t="n">
-        <v>6417537</v>
+        <v>6417510</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460769</v>
+        <v>122460572</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566727</v>
+        <v>566746</v>
       </c>
       <c r="R6" t="n">
-        <v>6417559</v>
+        <v>6417537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460353</v>
+        <v>122460786</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566758</v>
+        <v>566755</v>
       </c>
       <c r="R7" t="n">
-        <v>6417479</v>
+        <v>6417553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460344</v>
+        <v>122460716</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566761</v>
+        <v>566691</v>
       </c>
       <c r="R8" t="n">
-        <v>6417474</v>
+        <v>6417494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460478</v>
+        <v>122460440</v>
       </c>
       <c r="B9" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566761</v>
+        <v>566775</v>
       </c>
       <c r="R9" t="n">
-        <v>6417508</v>
+        <v>6417497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460462</v>
+        <v>122460420</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566759</v>
+        <v>566778</v>
       </c>
       <c r="R10" t="n">
-        <v>6417510</v>
+        <v>6417475</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460794</v>
+        <v>122460769</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566775</v>
+        <v>566727</v>
       </c>
       <c r="R11" t="n">
-        <v>6417541</v>
+        <v>6417559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460411</v>
+        <v>122460363</v>
       </c>
       <c r="B12" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566756</v>
+        <v>566758</v>
       </c>
       <c r="R12" t="n">
-        <v>6417478</v>
+        <v>6417476</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460420</v>
+        <v>122460929</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>57537</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,35 +1911,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1944,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566778</v>
+        <v>566622</v>
       </c>
       <c r="R13" t="n">
-        <v>6417475</v>
+        <v>6417518</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1988,7 +1995,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2007,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460934</v>
+        <v>122460839</v>
       </c>
       <c r="B14" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2019,39 +2025,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2059,13 +2061,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566622</v>
+        <v>566801</v>
       </c>
       <c r="R14" t="n">
-        <v>6417518</v>
+        <v>6417510</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,6 +2105,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2121,10 +2124,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460572</v>
+        <v>122460806</v>
       </c>
       <c r="B15" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566746</v>
+        <v>566775</v>
       </c>
       <c r="R15" t="n">
-        <v>6417537</v>
+        <v>6417541</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,10 +2235,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460363</v>
+        <v>122460344</v>
       </c>
       <c r="B16" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566758</v>
+        <v>566761</v>
       </c>
       <c r="R16" t="n">
-        <v>6417476</v>
+        <v>6417474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460427</v>
+        <v>122460450</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R17" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460440</v>
+        <v>122460727</v>
       </c>
       <c r="B18" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566775</v>
+        <v>566693</v>
       </c>
       <c r="R18" t="n">
-        <v>6417497</v>
+        <v>6417494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2568,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460400</v>
+        <v>122460830</v>
       </c>
       <c r="B19" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2613,10 +2616,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566747</v>
+        <v>566776</v>
       </c>
       <c r="R19" t="n">
-        <v>6417470</v>
+        <v>6417537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,10 +2679,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460760</v>
+        <v>122460427</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,10 +2727,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566688</v>
+        <v>566763</v>
       </c>
       <c r="R20" t="n">
-        <v>6417511</v>
+        <v>6417499</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,10 +2790,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460558</v>
+        <v>122460731</v>
       </c>
       <c r="B21" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2835,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566735</v>
+        <v>566693</v>
       </c>
       <c r="R21" t="n">
-        <v>6417522</v>
+        <v>6417493</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,10 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460581</v>
+        <v>122460491</v>
       </c>
       <c r="B22" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,10 +2949,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566740</v>
+        <v>566757</v>
       </c>
       <c r="R22" t="n">
-        <v>6417531</v>
+        <v>6417517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3009,10 +3012,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460450</v>
+        <v>122460919</v>
       </c>
       <c r="B23" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,10 +3060,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566761</v>
+        <v>566772</v>
       </c>
       <c r="R23" t="n">
-        <v>6417502</v>
+        <v>6417498</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,10 +3123,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460786</v>
+        <v>122460760</v>
       </c>
       <c r="B24" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,10 +3171,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566755</v>
+        <v>566688</v>
       </c>
       <c r="R24" t="n">
-        <v>6417553</v>
+        <v>6417511</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3231,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460929</v>
+        <v>122460434</v>
       </c>
       <c r="B25" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3243,39 +3246,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3283,13 +3282,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566622</v>
+        <v>566795</v>
       </c>
       <c r="R25" t="n">
         <v>6417518</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3327,6 +3326,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460491</v>
+        <v>122460522</v>
       </c>
       <c r="B26" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,7 +3384,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3393,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566757</v>
+        <v>566762</v>
       </c>
       <c r="R26" t="n">
-        <v>6417517</v>
+        <v>6417537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3456,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460743</v>
+        <v>122460916</v>
       </c>
       <c r="B27" t="n">
-        <v>91244</v>
+        <v>98244</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3468,38 +3472,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3507,10 +3508,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566698</v>
+        <v>566783</v>
       </c>
       <c r="R27" t="n">
-        <v>6417489</v>
+        <v>6417513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3570,10 +3571,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460916</v>
+        <v>122460581</v>
       </c>
       <c r="B28" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3618,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566783</v>
+        <v>566740</v>
       </c>
       <c r="R28" t="n">
-        <v>6417513</v>
+        <v>6417531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460716</v>
+        <v>122460743</v>
       </c>
       <c r="B29" t="n">
-        <v>98241</v>
+        <v>91247</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3693,35 +3694,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3729,10 +3733,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566691</v>
+        <v>566698</v>
       </c>
       <c r="R29" t="n">
-        <v>6417494</v>
+        <v>6417489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3795,7 +3799,7 @@
         <v>122460310</v>
       </c>
       <c r="B30" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460919</v>
+        <v>122460558</v>
       </c>
       <c r="B31" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3955,10 +3959,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566772</v>
+        <v>566735</v>
       </c>
       <c r="R31" t="n">
-        <v>6417498</v>
+        <v>6417522</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4018,10 +4022,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460727</v>
+        <v>122460478</v>
       </c>
       <c r="B32" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,10 +4070,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566693</v>
+        <v>566761</v>
       </c>
       <c r="R32" t="n">
-        <v>6417494</v>
+        <v>6417508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460731</v>
+        <v>122460400</v>
       </c>
       <c r="B33" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566693</v>
+        <v>566747</v>
       </c>
       <c r="R33" t="n">
-        <v>6417493</v>
+        <v>6417470</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,10 +4244,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460754</v>
+        <v>122460353</v>
       </c>
       <c r="B34" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566688</v>
+        <v>566758</v>
       </c>
       <c r="R34" t="n">
-        <v>6417499</v>
+        <v>6417479</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460934</v>
+        <v>122460839</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566622</v>
+        <v>566801</v>
       </c>
       <c r="R2" t="n">
-        <v>6417518</v>
+        <v>6417510</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460462</v>
+        <v>122460934</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566759</v>
+        <v>566622</v>
       </c>
       <c r="R5" t="n">
-        <v>6417510</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460572</v>
+        <v>122460434</v>
       </c>
       <c r="B6" t="n">
         <v>98244</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566746</v>
+        <v>566795</v>
       </c>
       <c r="R6" t="n">
-        <v>6417537</v>
+        <v>6417518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460786</v>
+        <v>122460509</v>
       </c>
       <c r="B7" t="n">
         <v>98244</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566755</v>
+        <v>566762</v>
       </c>
       <c r="R7" t="n">
-        <v>6417553</v>
+        <v>6417537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460716</v>
+        <v>122460363</v>
       </c>
       <c r="B8" t="n">
         <v>98244</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566691</v>
+        <v>566758</v>
       </c>
       <c r="R8" t="n">
-        <v>6417494</v>
+        <v>6417476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460440</v>
+        <v>122460794</v>
       </c>
       <c r="B9" t="n">
         <v>98244</v>
@@ -1506,7 +1506,7 @@
         <v>566775</v>
       </c>
       <c r="R9" t="n">
-        <v>6417497</v>
+        <v>6417541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460420</v>
+        <v>122460440</v>
       </c>
       <c r="B10" t="n">
         <v>98244</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566778</v>
+        <v>566775</v>
       </c>
       <c r="R10" t="n">
-        <v>6417475</v>
+        <v>6417497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460769</v>
+        <v>122460427</v>
       </c>
       <c r="B11" t="n">
         <v>98244</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566727</v>
+        <v>566763</v>
       </c>
       <c r="R11" t="n">
-        <v>6417559</v>
+        <v>6417499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460363</v>
+        <v>122460310</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1827,7 +1827,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1836,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566758</v>
+        <v>566794</v>
       </c>
       <c r="R12" t="n">
-        <v>6417476</v>
+        <v>6417463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460929</v>
+        <v>122460572</v>
       </c>
       <c r="B13" t="n">
-        <v>57537</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,39 +1915,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566622</v>
+        <v>566746</v>
       </c>
       <c r="R13" t="n">
-        <v>6417518</v>
+        <v>6417537</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2013,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460839</v>
+        <v>122460769</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2061,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566801</v>
+        <v>566727</v>
       </c>
       <c r="R14" t="n">
-        <v>6417510</v>
+        <v>6417559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2125,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460806</v>
+        <v>122460581</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2172,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566775</v>
+        <v>566740</v>
       </c>
       <c r="R15" t="n">
-        <v>6417541</v>
+        <v>6417531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460344</v>
+        <v>122460743</v>
       </c>
       <c r="B16" t="n">
-        <v>98244</v>
+        <v>91247</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2247,35 +2248,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2283,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566761</v>
+        <v>566698</v>
       </c>
       <c r="R16" t="n">
-        <v>6417474</v>
+        <v>6417489</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460450</v>
+        <v>122460344</v>
       </c>
       <c r="B17" t="n">
         <v>98244</v>
@@ -2397,7 +2401,7 @@
         <v>566761</v>
       </c>
       <c r="R17" t="n">
-        <v>6417502</v>
+        <v>6417474</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2461,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460727</v>
+        <v>122460830</v>
       </c>
       <c r="B18" t="n">
         <v>98244</v>
@@ -2505,10 +2509,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566693</v>
+        <v>566776</v>
       </c>
       <c r="R18" t="n">
-        <v>6417494</v>
+        <v>6417537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2572,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460830</v>
+        <v>122460353</v>
       </c>
       <c r="B19" t="n">
         <v>98244</v>
@@ -2616,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566776</v>
+        <v>566758</v>
       </c>
       <c r="R19" t="n">
-        <v>6417537</v>
+        <v>6417479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2679,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460427</v>
+        <v>122460450</v>
       </c>
       <c r="B20" t="n">
         <v>98244</v>
@@ -2727,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566763</v>
+        <v>566761</v>
       </c>
       <c r="R20" t="n">
-        <v>6417499</v>
+        <v>6417502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2794,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460731</v>
+        <v>122460919</v>
       </c>
       <c r="B21" t="n">
         <v>98244</v>
@@ -2838,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566693</v>
+        <v>566772</v>
       </c>
       <c r="R21" t="n">
-        <v>6417493</v>
+        <v>6417498</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2901,7 +2905,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460491</v>
+        <v>122460400</v>
       </c>
       <c r="B22" t="n">
         <v>98244</v>
@@ -2949,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566757</v>
+        <v>566747</v>
       </c>
       <c r="R22" t="n">
-        <v>6417517</v>
+        <v>6417470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,7 +3016,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460919</v>
+        <v>122460727</v>
       </c>
       <c r="B23" t="n">
         <v>98244</v>
@@ -3060,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566772</v>
+        <v>566693</v>
       </c>
       <c r="R23" t="n">
-        <v>6417498</v>
+        <v>6417494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,7 +3127,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460760</v>
+        <v>122460478</v>
       </c>
       <c r="B24" t="n">
         <v>98244</v>
@@ -3171,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566688</v>
+        <v>566761</v>
       </c>
       <c r="R24" t="n">
-        <v>6417511</v>
+        <v>6417508</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,7 +3238,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460434</v>
+        <v>122460760</v>
       </c>
       <c r="B25" t="n">
         <v>98244</v>
@@ -3282,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566795</v>
+        <v>566688</v>
       </c>
       <c r="R25" t="n">
-        <v>6417518</v>
+        <v>6417511</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3345,7 +3349,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460522</v>
+        <v>122460491</v>
       </c>
       <c r="B26" t="n">
         <v>98244</v>
@@ -3384,11 +3388,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566762</v>
+        <v>566757</v>
       </c>
       <c r="R26" t="n">
-        <v>6417537</v>
+        <v>6417517</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460581</v>
+        <v>122460716</v>
       </c>
       <c r="B28" t="n">
         <v>98244</v>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566740</v>
+        <v>566691</v>
       </c>
       <c r="R28" t="n">
-        <v>6417531</v>
+        <v>6417494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460743</v>
+        <v>122460558</v>
       </c>
       <c r="B29" t="n">
-        <v>91247</v>
+        <v>98244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3694,38 +3694,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3733,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566698</v>
+        <v>566735</v>
       </c>
       <c r="R29" t="n">
-        <v>6417489</v>
+        <v>6417522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,7 +3793,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460310</v>
+        <v>122460786</v>
       </c>
       <c r="B30" t="n">
         <v>98244</v>
@@ -3835,11 +3832,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3848,10 +3841,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566794</v>
+        <v>566755</v>
       </c>
       <c r="R30" t="n">
-        <v>6417463</v>
+        <v>6417553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,10 +3904,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460558</v>
+        <v>122460929</v>
       </c>
       <c r="B31" t="n">
-        <v>98244</v>
+        <v>57537</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3923,35 +3916,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3959,13 +3956,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566735</v>
+        <v>566622</v>
       </c>
       <c r="R31" t="n">
-        <v>6417522</v>
+        <v>6417518</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4003,7 +4000,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4022,7 +4018,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460478</v>
+        <v>122460420</v>
       </c>
       <c r="B32" t="n">
         <v>98244</v>
@@ -4070,10 +4066,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566761</v>
+        <v>566778</v>
       </c>
       <c r="R32" t="n">
-        <v>6417508</v>
+        <v>6417475</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4133,7 +4129,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460400</v>
+        <v>122460462</v>
       </c>
       <c r="B33" t="n">
         <v>98244</v>
@@ -4181,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566747</v>
+        <v>566759</v>
       </c>
       <c r="R33" t="n">
-        <v>6417470</v>
+        <v>6417510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460353</v>
+        <v>122460731</v>
       </c>
       <c r="B34" t="n">
         <v>98244</v>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566758</v>
+        <v>566693</v>
       </c>
       <c r="R34" t="n">
-        <v>6417479</v>
+        <v>6417493</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460310</v>
+        <v>122460572</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1827,11 +1827,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1840,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566794</v>
+        <v>566746</v>
       </c>
       <c r="R12" t="n">
-        <v>6417463</v>
+        <v>6417537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460572</v>
+        <v>122460769</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566746</v>
+        <v>566727</v>
       </c>
       <c r="R13" t="n">
-        <v>6417537</v>
+        <v>6417559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460769</v>
+        <v>122460581</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2062,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566727</v>
+        <v>566740</v>
       </c>
       <c r="R14" t="n">
-        <v>6417559</v>
+        <v>6417531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460581</v>
+        <v>122460310</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2164,7 +2160,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566740</v>
+        <v>566794</v>
       </c>
       <c r="R15" t="n">
-        <v>6417531</v>
+        <v>6417463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460754</v>
+        <v>122460411</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566688</v>
+        <v>566756</v>
       </c>
       <c r="R3" t="n">
-        <v>6417499</v>
+        <v>6417478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460411</v>
+        <v>122460754</v>
       </c>
       <c r="B4" t="n">
         <v>98244</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566756</v>
+        <v>566688</v>
       </c>
       <c r="R4" t="n">
-        <v>6417478</v>
+        <v>6417499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460572</v>
+        <v>122460310</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1827,7 +1827,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1836,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566746</v>
+        <v>566794</v>
       </c>
       <c r="R12" t="n">
-        <v>6417537</v>
+        <v>6417463</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1903,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460769</v>
+        <v>122460572</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -1947,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566727</v>
+        <v>566746</v>
       </c>
       <c r="R13" t="n">
-        <v>6417559</v>
+        <v>6417537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460581</v>
+        <v>122460769</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2058,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566740</v>
+        <v>566727</v>
       </c>
       <c r="R14" t="n">
-        <v>6417531</v>
+        <v>6417559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2125,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460310</v>
+        <v>122460581</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2160,11 +2164,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566794</v>
+        <v>566740</v>
       </c>
       <c r="R15" t="n">
-        <v>6417463</v>
+        <v>6417531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460934</v>
+        <v>122460434</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,39 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566622</v>
+        <v>566795</v>
       </c>
       <c r="R5" t="n">
         <v>6417518</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460434</v>
+        <v>122460934</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566795</v>
+        <v>566622</v>
       </c>
       <c r="R6" t="n">
         <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460310</v>
+        <v>122460572</v>
       </c>
       <c r="B12" t="n">
         <v>98244</v>
@@ -1827,11 +1827,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1840,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566794</v>
+        <v>566746</v>
       </c>
       <c r="R12" t="n">
-        <v>6417463</v>
+        <v>6417537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1899,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460572</v>
+        <v>122460769</v>
       </c>
       <c r="B13" t="n">
         <v>98244</v>
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566746</v>
+        <v>566727</v>
       </c>
       <c r="R13" t="n">
-        <v>6417537</v>
+        <v>6417559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2010,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460769</v>
+        <v>122460581</v>
       </c>
       <c r="B14" t="n">
         <v>98244</v>
@@ -2062,10 +2058,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566727</v>
+        <v>566740</v>
       </c>
       <c r="R14" t="n">
-        <v>6417559</v>
+        <v>6417531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460581</v>
+        <v>122460310</v>
       </c>
       <c r="B15" t="n">
         <v>98244</v>
@@ -2164,7 +2160,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566740</v>
+        <v>566794</v>
       </c>
       <c r="R15" t="n">
-        <v>6417531</v>
+        <v>6417463</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460434</v>
+        <v>122460934</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1020,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566795</v>
+        <v>566622</v>
       </c>
       <c r="R5" t="n">
         <v>6417518</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460934</v>
+        <v>122460434</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566622</v>
+        <v>566795</v>
       </c>
       <c r="R6" t="n">
         <v>6417518</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460839</v>
+        <v>122460929</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566801</v>
+        <v>566622</v>
       </c>
       <c r="R2" t="n">
-        <v>6417510</v>
+        <v>6417518</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460411</v>
+        <v>122460427</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566756</v>
+        <v>566763</v>
       </c>
       <c r="R3" t="n">
-        <v>6417478</v>
+        <v>6417499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460754</v>
+        <v>122460919</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566688</v>
+        <v>566772</v>
       </c>
       <c r="R4" t="n">
-        <v>6417499</v>
+        <v>6417498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460934</v>
+        <v>122460462</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,39 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566622</v>
+        <v>566759</v>
       </c>
       <c r="R5" t="n">
-        <v>6417518</v>
+        <v>6417510</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460434</v>
+        <v>122460522</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,7 +1161,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1170,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566795</v>
+        <v>566762</v>
       </c>
       <c r="R6" t="n">
-        <v>6417518</v>
+        <v>6417537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460509</v>
+        <v>122460839</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566762</v>
+        <v>566801</v>
       </c>
       <c r="R7" t="n">
-        <v>6417537</v>
+        <v>6417510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460363</v>
+        <v>122460934</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1360,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566758</v>
+        <v>566622</v>
       </c>
       <c r="R8" t="n">
-        <v>6417476</v>
+        <v>6417518</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1444,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460794</v>
+        <v>122460558</v>
       </c>
       <c r="B9" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566775</v>
+        <v>566735</v>
       </c>
       <c r="R9" t="n">
-        <v>6417541</v>
+        <v>6417522</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460440</v>
+        <v>122460786</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566775</v>
+        <v>566755</v>
       </c>
       <c r="R10" t="n">
-        <v>6417497</v>
+        <v>6417553</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,10 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460427</v>
+        <v>122460420</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566763</v>
+        <v>566778</v>
       </c>
       <c r="R11" t="n">
-        <v>6417499</v>
+        <v>6417475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460572</v>
+        <v>122460743</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,35 +1807,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1836,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566746</v>
+        <v>566698</v>
       </c>
       <c r="R12" t="n">
-        <v>6417537</v>
+        <v>6417489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,10 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460769</v>
+        <v>122460572</v>
       </c>
       <c r="B13" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566727</v>
+        <v>566746</v>
       </c>
       <c r="R13" t="n">
-        <v>6417559</v>
+        <v>6417537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2020,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460581</v>
+        <v>122460434</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566740</v>
+        <v>566795</v>
       </c>
       <c r="R14" t="n">
-        <v>6417531</v>
+        <v>6417518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460310</v>
+        <v>122460478</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,11 +2170,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2173,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566794</v>
+        <v>566761</v>
       </c>
       <c r="R15" t="n">
-        <v>6417463</v>
+        <v>6417508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460743</v>
+        <v>122460411</v>
       </c>
       <c r="B16" t="n">
-        <v>91247</v>
+        <v>98347</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,38 +2254,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,10 +2290,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566698</v>
+        <v>566756</v>
       </c>
       <c r="R16" t="n">
-        <v>6417489</v>
+        <v>6417478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460344</v>
+        <v>122460716</v>
       </c>
       <c r="B17" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566761</v>
+        <v>566691</v>
       </c>
       <c r="R17" t="n">
-        <v>6417474</v>
+        <v>6417494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460830</v>
+        <v>122460754</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566776</v>
+        <v>566688</v>
       </c>
       <c r="R18" t="n">
-        <v>6417537</v>
+        <v>6417499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2572,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460353</v>
+        <v>122460794</v>
       </c>
       <c r="B19" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566758</v>
+        <v>566775</v>
       </c>
       <c r="R19" t="n">
-        <v>6417479</v>
+        <v>6417541</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2683,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460450</v>
+        <v>122460310</v>
       </c>
       <c r="B20" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2722,7 +2725,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2731,10 +2738,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566761</v>
+        <v>566794</v>
       </c>
       <c r="R20" t="n">
-        <v>6417502</v>
+        <v>6417463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460919</v>
+        <v>122460731</v>
       </c>
       <c r="B21" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,10 +2849,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566772</v>
+        <v>566693</v>
       </c>
       <c r="R21" t="n">
-        <v>6417498</v>
+        <v>6417493</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460400</v>
+        <v>122460363</v>
       </c>
       <c r="B22" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2953,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566747</v>
+        <v>566758</v>
       </c>
       <c r="R22" t="n">
-        <v>6417470</v>
+        <v>6417476</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3023,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460727</v>
+        <v>122460491</v>
       </c>
       <c r="B23" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566693</v>
+        <v>566757</v>
       </c>
       <c r="R23" t="n">
-        <v>6417494</v>
+        <v>6417517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3127,10 +3134,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460478</v>
+        <v>122460353</v>
       </c>
       <c r="B24" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3175,10 +3182,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566761</v>
+        <v>566758</v>
       </c>
       <c r="R24" t="n">
-        <v>6417508</v>
+        <v>6417479</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3245,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460760</v>
+        <v>122460769</v>
       </c>
       <c r="B25" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,10 +3293,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566688</v>
+        <v>566727</v>
       </c>
       <c r="R25" t="n">
-        <v>6417511</v>
+        <v>6417559</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3349,10 +3356,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460491</v>
+        <v>122460916</v>
       </c>
       <c r="B26" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3397,10 +3404,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566757</v>
+        <v>566783</v>
       </c>
       <c r="R26" t="n">
-        <v>6417517</v>
+        <v>6417513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,10 +3467,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460916</v>
+        <v>122460727</v>
       </c>
       <c r="B27" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3508,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566783</v>
+        <v>566693</v>
       </c>
       <c r="R27" t="n">
-        <v>6417513</v>
+        <v>6417494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460716</v>
+        <v>122460450</v>
       </c>
       <c r="B28" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3619,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566691</v>
+        <v>566761</v>
       </c>
       <c r="R28" t="n">
-        <v>6417494</v>
+        <v>6417502</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,10 +3689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460558</v>
+        <v>122460830</v>
       </c>
       <c r="B29" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3730,10 +3737,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566735</v>
+        <v>566776</v>
       </c>
       <c r="R29" t="n">
-        <v>6417522</v>
+        <v>6417537</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460786</v>
+        <v>122460581</v>
       </c>
       <c r="B30" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566755</v>
+        <v>566740</v>
       </c>
       <c r="R30" t="n">
-        <v>6417553</v>
+        <v>6417531</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460929</v>
+        <v>122460400</v>
       </c>
       <c r="B31" t="n">
-        <v>57537</v>
+        <v>98347</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3916,39 +3923,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3956,13 +3959,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566622</v>
+        <v>566747</v>
       </c>
       <c r="R31" t="n">
-        <v>6417518</v>
+        <v>6417470</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4000,6 +4003,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4018,10 +4022,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460420</v>
+        <v>122460760</v>
       </c>
       <c r="B32" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,10 +4070,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566778</v>
+        <v>566688</v>
       </c>
       <c r="R32" t="n">
-        <v>6417475</v>
+        <v>6417511</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4129,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460462</v>
+        <v>122460344</v>
       </c>
       <c r="B33" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566759</v>
+        <v>566761</v>
       </c>
       <c r="R33" t="n">
-        <v>6417510</v>
+        <v>6417474</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4240,10 +4244,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460731</v>
+        <v>122460440</v>
       </c>
       <c r="B34" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4288,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566693</v>
+        <v>566775</v>
       </c>
       <c r="R34" t="n">
-        <v>6417493</v>
+        <v>6417497</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460363</v>
+        <v>122460491</v>
       </c>
       <c r="B22" t="n">
         <v>98347</v>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566758</v>
+        <v>566757</v>
       </c>
       <c r="R22" t="n">
-        <v>6417476</v>
+        <v>6417517</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460491</v>
+        <v>122460363</v>
       </c>
       <c r="B23" t="n">
         <v>98347</v>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566757</v>
+        <v>566758</v>
       </c>
       <c r="R23" t="n">
-        <v>6417517</v>
+        <v>6417476</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460929</v>
+        <v>122460363</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566622</v>
+        <v>566758</v>
       </c>
       <c r="R2" t="n">
-        <v>6417518</v>
+        <v>6417476</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460427</v>
+        <v>122460558</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566763</v>
+        <v>566735</v>
       </c>
       <c r="R3" t="n">
-        <v>6417499</v>
+        <v>6417522</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122460919</v>
+        <v>122460731</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566772</v>
+        <v>566693</v>
       </c>
       <c r="R4" t="n">
-        <v>6417498</v>
+        <v>6417493</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460462</v>
+        <v>122460916</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566759</v>
+        <v>566783</v>
       </c>
       <c r="R5" t="n">
-        <v>6417510</v>
+        <v>6417513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460522</v>
+        <v>122460427</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,11 +1158,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1174,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566762</v>
+        <v>566763</v>
       </c>
       <c r="R6" t="n">
-        <v>6417537</v>
+        <v>6417499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460839</v>
+        <v>122460434</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566801</v>
+        <v>566795</v>
       </c>
       <c r="R7" t="n">
-        <v>6417510</v>
+        <v>6417518</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460934</v>
+        <v>122460929</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,7 +1383,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1462,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460558</v>
+        <v>122460830</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566735</v>
+        <v>566776</v>
       </c>
       <c r="R9" t="n">
-        <v>6417522</v>
+        <v>6417537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460786</v>
+        <v>122460353</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566755</v>
+        <v>566758</v>
       </c>
       <c r="R10" t="n">
-        <v>6417553</v>
+        <v>6417479</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460420</v>
+        <v>122460478</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566778</v>
+        <v>566761</v>
       </c>
       <c r="R11" t="n">
-        <v>6417475</v>
+        <v>6417508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460743</v>
+        <v>122460581</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,38 +1800,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,10 +1836,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566698</v>
+        <v>566740</v>
       </c>
       <c r="R12" t="n">
-        <v>6417489</v>
+        <v>6417531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460572</v>
+        <v>122460420</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566746</v>
+        <v>566778</v>
       </c>
       <c r="R13" t="n">
-        <v>6417537</v>
+        <v>6417475</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460434</v>
+        <v>122460522</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,7 +2049,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2068,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566795</v>
+        <v>566762</v>
       </c>
       <c r="R14" t="n">
-        <v>6417518</v>
+        <v>6417537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460478</v>
+        <v>122460572</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,10 +2173,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566761</v>
+        <v>566746</v>
       </c>
       <c r="R15" t="n">
-        <v>6417508</v>
+        <v>6417537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,10 +2236,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460411</v>
+        <v>122460794</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,10 +2284,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566756</v>
+        <v>566775</v>
       </c>
       <c r="R16" t="n">
-        <v>6417478</v>
+        <v>6417541</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,10 +2347,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460716</v>
+        <v>122460769</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2401,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566691</v>
+        <v>566727</v>
       </c>
       <c r="R17" t="n">
-        <v>6417494</v>
+        <v>6417559</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460754</v>
+        <v>122460400</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566688</v>
+        <v>566747</v>
       </c>
       <c r="R18" t="n">
-        <v>6417499</v>
+        <v>6417470</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122460794</v>
+        <v>122460754</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2623,10 +2617,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566775</v>
+        <v>566688</v>
       </c>
       <c r="R19" t="n">
-        <v>6417541</v>
+        <v>6417499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460310</v>
+        <v>122460743</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2698,39 +2692,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2738,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566794</v>
+        <v>566698</v>
       </c>
       <c r="R20" t="n">
-        <v>6417463</v>
+        <v>6417489</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460731</v>
+        <v>122460344</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2849,10 +2842,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566693</v>
+        <v>566761</v>
       </c>
       <c r="R21" t="n">
-        <v>6417493</v>
+        <v>6417474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460491</v>
+        <v>122460450</v>
       </c>
       <c r="B22" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566757</v>
+        <v>566761</v>
       </c>
       <c r="R22" t="n">
-        <v>6417517</v>
+        <v>6417502</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,10 +3016,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460363</v>
+        <v>122460440</v>
       </c>
       <c r="B23" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3071,10 +3064,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566758</v>
+        <v>566775</v>
       </c>
       <c r="R23" t="n">
-        <v>6417476</v>
+        <v>6417497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3134,10 +3127,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460353</v>
+        <v>122460919</v>
       </c>
       <c r="B24" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3182,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566758</v>
+        <v>566772</v>
       </c>
       <c r="R24" t="n">
-        <v>6417479</v>
+        <v>6417498</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3245,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460769</v>
+        <v>122460934</v>
       </c>
       <c r="B25" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3257,35 +3250,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3293,13 +3290,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566727</v>
+        <v>566622</v>
       </c>
       <c r="R25" t="n">
-        <v>6417559</v>
+        <v>6417518</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3334,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3356,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460916</v>
+        <v>122460411</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3404,10 +3400,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566783</v>
+        <v>566756</v>
       </c>
       <c r="R26" t="n">
-        <v>6417513</v>
+        <v>6417478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3467,10 +3463,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460727</v>
+        <v>122460310</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3506,7 +3502,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566693</v>
+        <v>566794</v>
       </c>
       <c r="R27" t="n">
-        <v>6417494</v>
+        <v>6417463</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460450</v>
+        <v>122460839</v>
       </c>
       <c r="B28" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566761</v>
+        <v>566801</v>
       </c>
       <c r="R28" t="n">
-        <v>6417502</v>
+        <v>6417510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460830</v>
+        <v>122460491</v>
       </c>
       <c r="B29" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566776</v>
+        <v>566757</v>
       </c>
       <c r="R29" t="n">
-        <v>6417537</v>
+        <v>6417517</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460581</v>
+        <v>122460462</v>
       </c>
       <c r="B30" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566740</v>
+        <v>566759</v>
       </c>
       <c r="R30" t="n">
-        <v>6417531</v>
+        <v>6417510</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460400</v>
+        <v>122460786</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566747</v>
+        <v>566755</v>
       </c>
       <c r="R31" t="n">
-        <v>6417470</v>
+        <v>6417553</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460760</v>
+        <v>122460716</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566688</v>
+        <v>566691</v>
       </c>
       <c r="R32" t="n">
-        <v>6417511</v>
+        <v>6417494</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460344</v>
+        <v>122460727</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,10 +4181,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566761</v>
+        <v>566693</v>
       </c>
       <c r="R33" t="n">
-        <v>6417474</v>
+        <v>6417494</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460440</v>
+        <v>122460760</v>
       </c>
       <c r="B34" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566775</v>
+        <v>566688</v>
       </c>
       <c r="R34" t="n">
-        <v>6417497</v>
+        <v>6417511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 954-2025 artfynd.xlsx
+++ b/artfynd/A 954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122460363</v>
+        <v>122460310</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -714,7 +714,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566758</v>
+        <v>566794</v>
       </c>
       <c r="R2" t="n">
-        <v>6417476</v>
+        <v>6417463</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122460558</v>
+        <v>122460581</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566735</v>
+        <v>566740</v>
       </c>
       <c r="R3" t="n">
-        <v>6417522</v>
+        <v>6417531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,7 +1012,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122460916</v>
+        <v>122460434</v>
       </c>
       <c r="B5" t="n">
         <v>98355</v>
@@ -1056,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566783</v>
+        <v>566795</v>
       </c>
       <c r="R5" t="n">
-        <v>6417513</v>
+        <v>6417518</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122460427</v>
+        <v>122460558</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1167,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566763</v>
+        <v>566735</v>
       </c>
       <c r="R6" t="n">
-        <v>6417499</v>
+        <v>6417522</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1234,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122460434</v>
+        <v>122460478</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566795</v>
+        <v>566761</v>
       </c>
       <c r="R7" t="n">
-        <v>6417518</v>
+        <v>6417508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122460929</v>
+        <v>122460919</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,39 +1357,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566622</v>
+        <v>566772</v>
       </c>
       <c r="R8" t="n">
-        <v>6417518</v>
+        <v>6417498</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,6 +1437,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1455,7 +1456,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122460830</v>
+        <v>122460344</v>
       </c>
       <c r="B9" t="n">
         <v>98355</v>
@@ -1503,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566776</v>
+        <v>566761</v>
       </c>
       <c r="R9" t="n">
-        <v>6417537</v>
+        <v>6417474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122460353</v>
+        <v>122460450</v>
       </c>
       <c r="B10" t="n">
         <v>98355</v>
@@ -1614,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566758</v>
+        <v>566761</v>
       </c>
       <c r="R10" t="n">
-        <v>6417479</v>
+        <v>6417502</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122460478</v>
+        <v>122460769</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1725,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566761</v>
+        <v>566727</v>
       </c>
       <c r="R11" t="n">
-        <v>6417508</v>
+        <v>6417559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1789,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122460581</v>
+        <v>122460509</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1836,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566740</v>
+        <v>566762</v>
       </c>
       <c r="R12" t="n">
-        <v>6417531</v>
+        <v>6417537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122460420</v>
+        <v>122460806</v>
       </c>
       <c r="B13" t="n">
         <v>98355</v>
@@ -1947,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566778</v>
+        <v>566775</v>
       </c>
       <c r="R13" t="n">
-        <v>6417475</v>
+        <v>6417541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2011,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122460522</v>
+        <v>122460716</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -2049,11 +2050,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2062,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566762</v>
+        <v>566691</v>
       </c>
       <c r="R14" t="n">
-        <v>6417537</v>
+        <v>6417494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2122,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122460572</v>
+        <v>122460760</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2173,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566746</v>
+        <v>566688</v>
       </c>
       <c r="R15" t="n">
-        <v>6417537</v>
+        <v>6417511</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122460794</v>
+        <v>122460400</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2284,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566775</v>
+        <v>566747</v>
       </c>
       <c r="R16" t="n">
-        <v>6417541</v>
+        <v>6417470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2344,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122460769</v>
+        <v>122460830</v>
       </c>
       <c r="B17" t="n">
         <v>98355</v>
@@ -2395,10 +2392,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566727</v>
+        <v>566776</v>
       </c>
       <c r="R17" t="n">
-        <v>6417559</v>
+        <v>6417537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122460400</v>
+        <v>122460491</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2506,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566747</v>
+        <v>566757</v>
       </c>
       <c r="R18" t="n">
-        <v>6417470</v>
+        <v>6417517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2680,10 +2677,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122460743</v>
+        <v>122460572</v>
       </c>
       <c r="B20" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,38 +2689,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2731,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566698</v>
+        <v>566746</v>
       </c>
       <c r="R20" t="n">
-        <v>6417489</v>
+        <v>6417537</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2794,7 +2788,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122460344</v>
+        <v>122460353</v>
       </c>
       <c r="B21" t="n">
         <v>98355</v>
@@ -2842,10 +2836,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566761</v>
+        <v>566758</v>
       </c>
       <c r="R21" t="n">
-        <v>6417474</v>
+        <v>6417479</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2905,7 +2899,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122460450</v>
+        <v>122460363</v>
       </c>
       <c r="B22" t="n">
         <v>98355</v>
@@ -2953,10 +2947,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566761</v>
+        <v>566758</v>
       </c>
       <c r="R22" t="n">
-        <v>6417502</v>
+        <v>6417476</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122460440</v>
+        <v>122460929</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,35 +3022,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3064,13 +3062,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566775</v>
+        <v>566622</v>
       </c>
       <c r="R23" t="n">
-        <v>6417497</v>
+        <v>6417518</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3108,7 +3106,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3127,7 +3124,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122460919</v>
+        <v>122460440</v>
       </c>
       <c r="B24" t="n">
         <v>98355</v>
@@ -3175,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566772</v>
+        <v>566775</v>
       </c>
       <c r="R24" t="n">
-        <v>6417498</v>
+        <v>6417497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122460934</v>
+        <v>122460462</v>
       </c>
       <c r="B25" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3250,39 +3247,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3290,13 +3283,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566622</v>
+        <v>566759</v>
       </c>
       <c r="R25" t="n">
-        <v>6417518</v>
+        <v>6417510</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3334,6 +3327,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3352,7 +3346,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122460411</v>
+        <v>122460786</v>
       </c>
       <c r="B26" t="n">
         <v>98355</v>
@@ -3400,10 +3394,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566756</v>
+        <v>566755</v>
       </c>
       <c r="R26" t="n">
-        <v>6417478</v>
+        <v>6417553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,10 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122460310</v>
+        <v>122460934</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3475,39 +3469,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3515,13 +3509,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566794</v>
+        <v>566622</v>
       </c>
       <c r="R27" t="n">
-        <v>6417463</v>
+        <v>6417518</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3559,7 +3553,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3578,7 +3571,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122460839</v>
+        <v>122460427</v>
       </c>
       <c r="B28" t="n">
         <v>98355</v>
@@ -3626,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566801</v>
+        <v>566763</v>
       </c>
       <c r="R28" t="n">
-        <v>6417510</v>
+        <v>6417499</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3689,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122460491</v>
+        <v>122460839</v>
       </c>
       <c r="B29" t="n">
         <v>98355</v>
@@ -3737,10 +3730,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566757</v>
+        <v>566801</v>
       </c>
       <c r="R29" t="n">
-        <v>6417517</v>
+        <v>6417510</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3800,7 +3793,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122460462</v>
+        <v>122460916</v>
       </c>
       <c r="B30" t="n">
         <v>98355</v>
@@ -3848,10 +3841,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566759</v>
+        <v>566783</v>
       </c>
       <c r="R30" t="n">
-        <v>6417510</v>
+        <v>6417513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,7 +3904,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122460786</v>
+        <v>122460727</v>
       </c>
       <c r="B31" t="n">
         <v>98355</v>
@@ -3959,10 +3952,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566755</v>
+        <v>566693</v>
       </c>
       <c r="R31" t="n">
-        <v>6417553</v>
+        <v>6417494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4022,7 +4015,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122460716</v>
+        <v>122460420</v>
       </c>
       <c r="B32" t="n">
         <v>98355</v>
@@ -4070,10 +4063,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566691</v>
+        <v>566778</v>
       </c>
       <c r="R32" t="n">
-        <v>6417494</v>
+        <v>6417475</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4133,10 +4126,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122460727</v>
+        <v>122460743</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4145,35 +4138,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4181,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566693</v>
+        <v>566698</v>
       </c>
       <c r="R33" t="n">
-        <v>6417494</v>
+        <v>6417489</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122460760</v>
+        <v>122460411</v>
       </c>
       <c r="B34" t="n">
         <v>98355</v>
@@ -4292,10 +4288,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566688</v>
+        <v>566756</v>
       </c>
       <c r="R34" t="n">
-        <v>6417511</v>
+        <v>6417478</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
